--- a/gstdatabase/GSTR-3B-2018-2019.xlsx
+++ b/gstdatabase/GSTR-3B-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D038F86-0655-4890-9A62-3B94BF92FE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2257CD6-ED67-467C-B02B-67AA584CF48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -388,23 +388,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -414,6 +405,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -754,12 +754,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -776,11 +776,11 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -806,14 +806,14 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
     </row>
     <row r="8" spans="1:62" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -905,7 +905,7 @@
       <c r="BJ8" s="19"/>
     </row>
     <row r="9" spans="1:62" s="11" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="19"/>
       <c r="C9" s="12" t="s">
         <v>3</v>
@@ -1527,14 +1527,14 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" si="0"/>
-        <v>142860</v>
+        <v>142861</v>
       </c>
       <c r="F12" s="7">
-        <v>257212</v>
+        <v>257213</v>
       </c>
       <c r="G12" s="9">
         <f t="shared" si="1"/>
-        <v>0.94468072603333408</v>
+        <v>0.94468439880414579</v>
       </c>
       <c r="H12" s="4">
         <v>280783</v>
@@ -2070,14 +2070,14 @@
       </c>
       <c r="AN14" s="10">
         <f t="shared" si="14"/>
-        <v>33136</v>
+        <v>33137</v>
       </c>
       <c r="AO14" s="7">
-        <v>107462</v>
+        <v>107463</v>
       </c>
       <c r="AP14" s="9">
         <f t="shared" si="15"/>
-        <v>0.870017892273938</v>
+        <v>0.8700259883254936</v>
       </c>
       <c r="AQ14" s="4">
         <v>123658</v>
@@ -2087,14 +2087,14 @@
       </c>
       <c r="AS14" s="10">
         <f t="shared" si="16"/>
-        <v>34408</v>
+        <v>34409</v>
       </c>
       <c r="AT14" s="7">
-        <v>108846</v>
+        <v>108847</v>
       </c>
       <c r="AU14" s="9">
         <f t="shared" si="17"/>
-        <v>0.88021802066991217</v>
+        <v>0.88022610749001273</v>
       </c>
       <c r="AV14" s="6">
         <v>124350</v>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="AX14" s="10">
         <f t="shared" si="18"/>
-        <v>41634</v>
+        <v>41635</v>
       </c>
       <c r="AY14" s="7">
-        <v>110142</v>
+        <v>110143</v>
       </c>
       <c r="AZ14" s="9">
         <f t="shared" si="19"/>
-        <v>0.88574185765983116</v>
+        <v>0.88574989947728189</v>
       </c>
       <c r="BA14" s="6">
         <v>126171</v>
@@ -2121,14 +2121,14 @@
       </c>
       <c r="BC14" s="10">
         <f t="shared" si="20"/>
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="BD14" s="7">
-        <v>111496</v>
+        <v>111497</v>
       </c>
       <c r="BE14" s="9">
         <f t="shared" si="21"/>
-        <v>0.88368959586592799</v>
+        <v>0.88369752161748738</v>
       </c>
       <c r="BF14" s="6">
         <v>128280</v>
@@ -2138,14 +2138,14 @@
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="22"/>
-        <v>47280</v>
+        <v>47282</v>
       </c>
       <c r="BI14" s="7">
-        <v>112948</v>
+        <v>112950</v>
       </c>
       <c r="BJ14" s="9">
         <f t="shared" si="23"/>
-        <v>0.88048019956345491</v>
+        <v>0.88049579045837234</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2528,14 +2528,14 @@
       </c>
       <c r="AX16" s="10">
         <f t="shared" si="18"/>
-        <v>229716</v>
+        <v>229717</v>
       </c>
       <c r="AY16" s="7">
-        <v>608060</v>
+        <v>608061</v>
       </c>
       <c r="AZ16" s="9">
         <f t="shared" si="19"/>
-        <v>0.85528416403519258</v>
+        <v>0.85528557061376054</v>
       </c>
       <c r="BA16" s="6">
         <v>719691</v>
@@ -2545,14 +2545,14 @@
       </c>
       <c r="BC16" s="10">
         <f t="shared" si="20"/>
-        <v>145971</v>
+        <v>145972</v>
       </c>
       <c r="BD16" s="7">
-        <v>612254</v>
+        <v>612255</v>
       </c>
       <c r="BE16" s="9">
         <f t="shared" si="21"/>
-        <v>0.85071787753355255</v>
+        <v>0.85071926701876222</v>
       </c>
       <c r="BF16" s="6">
         <v>730364</v>
@@ -2562,14 +2562,14 @@
       </c>
       <c r="BH16" s="10">
         <f t="shared" si="22"/>
-        <v>266674</v>
+        <v>266675</v>
       </c>
       <c r="BI16" s="7">
-        <v>617123</v>
+        <v>617124</v>
       </c>
       <c r="BJ16" s="9">
         <f t="shared" si="23"/>
-        <v>0.84495265374525574</v>
+        <v>0.84495402292555488</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2587,14 +2587,14 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" si="0"/>
-        <v>242313</v>
+        <v>242315</v>
       </c>
       <c r="F17" s="7">
-        <v>439551</v>
+        <v>439553</v>
       </c>
       <c r="G17" s="9">
         <f t="shared" si="1"/>
-        <v>0.93721095354147876</v>
+        <v>0.93721521794289542</v>
       </c>
       <c r="H17" s="4">
         <v>489282</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="J17" s="10">
         <f t="shared" si="2"/>
-        <v>123100</v>
+        <v>123101</v>
       </c>
       <c r="K17" s="7">
-        <v>447857</v>
+        <v>447858</v>
       </c>
       <c r="L17" s="9">
         <f t="shared" si="3"/>
-        <v>0.91533512371188808</v>
+        <v>0.91533716752302352</v>
       </c>
       <c r="M17" s="4">
         <v>500417</v>
@@ -2621,14 +2621,14 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="4"/>
-        <v>130682</v>
+        <v>130683</v>
       </c>
       <c r="P17" s="7">
-        <v>454475</v>
+        <v>454476</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="5"/>
-        <v>0.9081925673987894</v>
+        <v>0.90819456573217938</v>
       </c>
       <c r="R17" s="4">
         <v>507666</v>
@@ -2638,14 +2638,14 @@
       </c>
       <c r="T17" s="10">
         <f t="shared" si="6"/>
-        <v>100288</v>
+        <v>100289</v>
       </c>
       <c r="U17" s="7">
-        <v>459364</v>
+        <v>459365</v>
       </c>
       <c r="V17" s="9">
         <f t="shared" si="7"/>
-        <v>0.90485476671669951</v>
+        <v>0.90485673651574061</v>
       </c>
       <c r="W17" s="4">
         <v>515229</v>
@@ -2655,14 +2655,14 @@
       </c>
       <c r="Y17" s="10">
         <f t="shared" si="8"/>
-        <v>145542</v>
+        <v>145545</v>
       </c>
       <c r="Z17" s="7">
-        <v>465276</v>
+        <v>465279</v>
       </c>
       <c r="AA17" s="9">
         <f t="shared" si="9"/>
-        <v>0.90304699463733606</v>
+        <v>0.90305281729095221</v>
       </c>
       <c r="AB17" s="4">
         <v>511436</v>
@@ -2672,14 +2672,14 @@
       </c>
       <c r="AD17" s="10">
         <f t="shared" si="10"/>
-        <v>110369</v>
+        <v>110370</v>
       </c>
       <c r="AE17" s="7">
-        <v>470673</v>
+        <v>470674</v>
       </c>
       <c r="AF17" s="9">
         <f t="shared" si="11"/>
-        <v>0.92029696775354097</v>
+        <v>0.9202989230324029</v>
       </c>
       <c r="AG17" s="4">
         <v>520284</v>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="AI17" s="10">
         <f t="shared" si="12"/>
-        <v>143339</v>
+        <v>143340</v>
       </c>
       <c r="AJ17" s="7">
-        <v>474889</v>
+        <v>474890</v>
       </c>
       <c r="AK17" s="9">
         <f t="shared" si="13"/>
-        <v>0.91274957523198863</v>
+        <v>0.91275149725918925</v>
       </c>
       <c r="AL17" s="4">
         <v>524911</v>
@@ -2706,14 +2706,14 @@
       </c>
       <c r="AN17" s="10">
         <f t="shared" si="14"/>
-        <v>119145</v>
+        <v>119146</v>
       </c>
       <c r="AO17" s="7">
-        <v>474446</v>
+        <v>474447</v>
       </c>
       <c r="AP17" s="9">
         <f t="shared" si="15"/>
-        <v>0.90385989243890874</v>
+        <v>0.90386179752377072</v>
       </c>
       <c r="AQ17" s="4">
         <v>530594</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>127499</v>
+        <v>127502</v>
       </c>
       <c r="AT17" s="7">
-        <v>478896</v>
+        <v>478899</v>
       </c>
       <c r="AU17" s="9">
         <f t="shared" si="17"/>
-        <v>0.90256580360878558</v>
+        <v>0.90257145764935143</v>
       </c>
       <c r="AV17" s="6">
         <v>538347</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>162547</v>
+        <v>162548</v>
       </c>
       <c r="AY17" s="7">
-        <v>483870</v>
+        <v>483871</v>
       </c>
       <c r="AZ17" s="9">
         <f t="shared" si="19"/>
-        <v>0.89880690335415636</v>
+        <v>0.89880876089213835</v>
       </c>
       <c r="BA17" s="6">
         <v>545177</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>100821</v>
+        <v>100823</v>
       </c>
       <c r="BD17" s="7">
-        <v>489106</v>
+        <v>489108</v>
       </c>
       <c r="BE17" s="9">
         <f t="shared" si="21"/>
-        <v>0.89715083358248793</v>
+        <v>0.89715450211582659</v>
       </c>
       <c r="BF17" s="6">
         <v>551432</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>209685</v>
+        <v>209688</v>
       </c>
       <c r="BI17" s="7">
-        <v>493400</v>
+        <v>493403</v>
       </c>
       <c r="BJ17" s="9">
         <f t="shared" si="23"/>
-        <v>0.89476127609569267</v>
+        <v>0.89476671647637429</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>416755</v>
+        <v>416758</v>
       </c>
       <c r="F18" s="7">
-        <v>867164</v>
+        <v>867167</v>
       </c>
       <c r="G18" s="9">
         <f t="shared" si="1"/>
-        <v>0.9199839590233676</v>
+        <v>0.91998714175682639</v>
       </c>
       <c r="H18" s="4">
         <v>980551</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>214879</v>
+        <v>214880</v>
       </c>
       <c r="K18" s="7">
-        <v>889302</v>
+        <v>889303</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="3"/>
-        <v>0.90694109740339868</v>
+        <v>0.90694211723816509</v>
       </c>
       <c r="M18" s="4">
         <v>1006440</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>222984</v>
+        <v>222985</v>
       </c>
       <c r="P18" s="7">
-        <v>903684</v>
+        <v>903685</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="5"/>
-        <v>0.89790151424824127</v>
+        <v>0.89790250784944958</v>
       </c>
       <c r="R18" s="4">
         <v>1025384</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>174916</v>
+        <v>174919</v>
       </c>
       <c r="U18" s="7">
-        <v>917014</v>
+        <v>917017</v>
       </c>
       <c r="V18" s="9">
         <f t="shared" si="7"/>
-        <v>0.89431276477885358</v>
+        <v>0.89431569051204229</v>
       </c>
       <c r="W18" s="4">
         <v>1044299</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>254594</v>
+        <v>254595</v>
       </c>
       <c r="Z18" s="7">
-        <v>930885</v>
+        <v>930886</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="9"/>
-        <v>0.89139700411472189</v>
+        <v>0.89139796169487862</v>
       </c>
       <c r="AB18" s="4">
         <v>1050898</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>187474</v>
+        <v>187476</v>
       </c>
       <c r="AE18" s="7">
-        <v>943111</v>
+        <v>943113</v>
       </c>
       <c r="AF18" s="9">
         <f t="shared" si="11"/>
-        <v>0.89743343312100698</v>
+        <v>0.89743533625527883</v>
       </c>
       <c r="AG18" s="4">
         <v>1062525</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>256111</v>
+        <v>256112</v>
       </c>
       <c r="AJ18" s="7">
-        <v>957860</v>
+        <v>957861</v>
       </c>
       <c r="AK18" s="9">
         <f t="shared" si="13"/>
-        <v>0.90149408249217666</v>
+        <v>0.90149502364650247</v>
       </c>
       <c r="AL18" s="4">
         <v>1073550</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>218723</v>
+        <v>218725</v>
       </c>
       <c r="AO18" s="7">
-        <v>956526</v>
+        <v>956528</v>
       </c>
       <c r="AP18" s="9">
         <f t="shared" si="15"/>
-        <v>0.89099343300265477</v>
+        <v>0.89099529598062499</v>
       </c>
       <c r="AQ18" s="4">
         <v>1080975</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>233198</v>
+        <v>233200</v>
       </c>
       <c r="AT18" s="7">
-        <v>967312</v>
+        <v>967314</v>
       </c>
       <c r="AU18" s="9">
         <f t="shared" si="17"/>
-        <v>0.89485140729434076</v>
+        <v>0.89485325747588984</v>
       </c>
       <c r="AV18" s="6">
         <v>1090269</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="18"/>
-        <v>321385</v>
+        <v>321388</v>
       </c>
       <c r="AY18" s="7">
-        <v>975592</v>
+        <v>975595</v>
       </c>
       <c r="AZ18" s="9">
         <f t="shared" si="19"/>
-        <v>0.89481770095270063</v>
+        <v>0.89482045256721043</v>
       </c>
       <c r="BA18" s="6">
         <v>1099973</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>196053</v>
+        <v>196057</v>
       </c>
       <c r="BD18" s="7">
-        <v>982906</v>
+        <v>982910</v>
       </c>
       <c r="BE18" s="9">
         <f t="shared" si="21"/>
-        <v>0.89357284224249145</v>
+        <v>0.89357647869538614</v>
       </c>
       <c r="BF18" s="6">
         <v>1108438</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>378204</v>
+        <v>378208</v>
       </c>
       <c r="BI18" s="7">
-        <v>990070</v>
+        <v>990074</v>
       </c>
       <c r="BJ18" s="9">
         <f t="shared" si="23"/>
-        <v>0.89321188916294825</v>
+        <v>0.89321549784471477</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="8"/>
-        <v>90220</v>
+        <v>90221</v>
       </c>
       <c r="Z19" s="7">
-        <v>235052</v>
+        <v>235053</v>
       </c>
       <c r="AA19" s="9">
         <f t="shared" si="9"/>
-        <v>0.86629565473777315</v>
+        <v>0.86629934028673572</v>
       </c>
       <c r="AB19" s="4">
         <v>274935</v>
@@ -3130,14 +3130,14 @@
       </c>
       <c r="AN19" s="10">
         <f t="shared" si="14"/>
-        <v>83206</v>
+        <v>83207</v>
       </c>
       <c r="AO19" s="7">
-        <v>242962</v>
+        <v>242963</v>
       </c>
       <c r="AP19" s="9">
         <f t="shared" si="15"/>
-        <v>0.85588876637627653</v>
+        <v>0.85589228910314896</v>
       </c>
       <c r="AQ19" s="4">
         <v>287360</v>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="AS19" s="10">
         <f t="shared" si="16"/>
-        <v>82623</v>
+        <v>82624</v>
       </c>
       <c r="AT19" s="7">
-        <v>247305</v>
+        <v>247306</v>
       </c>
       <c r="AU19" s="9">
         <f t="shared" si="17"/>
-        <v>0.86061038418708236</v>
+        <v>0.86061386414253893</v>
       </c>
       <c r="AV19" s="6">
         <v>294065</v>
@@ -3164,14 +3164,14 @@
       </c>
       <c r="AX19" s="10">
         <f t="shared" si="18"/>
-        <v>100121</v>
+        <v>100122</v>
       </c>
       <c r="AY19" s="7">
-        <v>252082</v>
+        <v>252083</v>
       </c>
       <c r="AZ19" s="9">
         <f t="shared" si="19"/>
-        <v>0.85723224457177838</v>
+        <v>0.85723564518048734</v>
       </c>
       <c r="BA19" s="6">
         <v>298702</v>
@@ -3181,14 +3181,14 @@
       </c>
       <c r="BC19" s="10">
         <f t="shared" si="20"/>
-        <v>75482</v>
+        <v>75484</v>
       </c>
       <c r="BD19" s="7">
-        <v>255958</v>
+        <v>255960</v>
       </c>
       <c r="BE19" s="9">
         <f t="shared" si="21"/>
-        <v>0.85690085771102975</v>
+        <v>0.85690755334748347</v>
       </c>
       <c r="BF19" s="6">
         <v>304255</v>
@@ -3198,14 +3198,14 @@
       </c>
       <c r="BH19" s="10">
         <f t="shared" si="22"/>
-        <v>125451</v>
+        <v>125454</v>
       </c>
       <c r="BI19" s="7">
-        <v>258462</v>
+        <v>258465</v>
       </c>
       <c r="BJ19" s="9">
         <f t="shared" si="23"/>
-        <v>0.84949138058536422</v>
+        <v>0.84950124073556721</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="22"/>
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="BI21" s="7">
-        <v>8351</v>
+        <v>8352</v>
       </c>
       <c r="BJ21" s="9">
         <f t="shared" si="23"/>
-        <v>0.77777777777777779</v>
+        <v>0.7778709136630344</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3893,14 +3893,14 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="4"/>
-        <v>4285</v>
+        <v>4286</v>
       </c>
       <c r="P23" s="7">
-        <v>7176</v>
+        <v>7177</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="5"/>
-        <v>0.7602500264858566</v>
+        <v>0.760355969912067</v>
       </c>
       <c r="R23" s="4">
         <v>9686</v>
@@ -4707,14 +4707,14 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" si="0"/>
-        <v>75970</v>
+        <v>75971</v>
       </c>
       <c r="F27" s="7">
-        <v>104527</v>
+        <v>104528</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" si="1"/>
-        <v>0.82744508212942802</v>
+        <v>0.82745299821887985</v>
       </c>
       <c r="H27" s="4">
         <v>130935</v>
@@ -4724,14 +4724,14 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="2"/>
-        <v>52738</v>
+        <v>52739</v>
       </c>
       <c r="K27" s="7">
-        <v>107535</v>
+        <v>107536</v>
       </c>
       <c r="L27" s="9">
         <f t="shared" si="3"/>
-        <v>0.82128537060373463</v>
+        <v>0.82129300798105931</v>
       </c>
       <c r="M27" s="4">
         <v>136177</v>
@@ -4741,14 +4741,14 @@
       </c>
       <c r="O27" s="10">
         <f t="shared" si="4"/>
-        <v>53059</v>
+        <v>53060</v>
       </c>
       <c r="P27" s="7">
-        <v>109973</v>
+        <v>109974</v>
       </c>
       <c r="Q27" s="9">
         <f t="shared" si="5"/>
-        <v>0.80757396623512046</v>
+        <v>0.80758130961909869</v>
       </c>
       <c r="R27" s="4">
         <v>139635</v>
@@ -4758,14 +4758,14 @@
       </c>
       <c r="T27" s="10">
         <f t="shared" si="6"/>
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="U27" s="7">
-        <v>112368</v>
+        <v>112369</v>
       </c>
       <c r="V27" s="9">
         <f t="shared" si="7"/>
-        <v>0.80472660865828771</v>
+        <v>0.80473377018655778</v>
       </c>
       <c r="W27" s="4">
         <v>142710</v>
@@ -4775,14 +4775,14 @@
       </c>
       <c r="Y27" s="10">
         <f t="shared" si="8"/>
-        <v>56034</v>
+        <v>56035</v>
       </c>
       <c r="Z27" s="7">
-        <v>114335</v>
+        <v>114336</v>
       </c>
       <c r="AA27" s="9">
         <f t="shared" si="9"/>
-        <v>0.80117020531147076</v>
+        <v>0.80117721252890473</v>
       </c>
       <c r="AB27" s="4">
         <v>144015</v>
@@ -4792,14 +4792,14 @@
       </c>
       <c r="AD27" s="10">
         <f t="shared" si="10"/>
-        <v>52738</v>
+        <v>52739</v>
       </c>
       <c r="AE27" s="7">
-        <v>115716</v>
+        <v>115717</v>
       </c>
       <c r="AF27" s="9">
         <f t="shared" si="11"/>
-        <v>0.80349963545464009</v>
+        <v>0.80350657917578028</v>
       </c>
       <c r="AG27" s="4">
         <v>146365</v>
@@ -4809,14 +4809,14 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="12"/>
-        <v>56534</v>
+        <v>56535</v>
       </c>
       <c r="AJ27" s="7">
-        <v>117013</v>
+        <v>117014</v>
       </c>
       <c r="AK27" s="9">
         <f t="shared" si="13"/>
-        <v>0.79946025347589933</v>
+        <v>0.79946708571038161</v>
       </c>
       <c r="AL27" s="4">
         <v>148564</v>
@@ -4826,14 +4826,14 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="14"/>
-        <v>51224</v>
+        <v>51226</v>
       </c>
       <c r="AO27" s="7">
-        <v>116560</v>
+        <v>116562</v>
       </c>
       <c r="AP27" s="9">
         <f t="shared" si="15"/>
-        <v>0.78457769042298264</v>
+        <v>0.78459115263455481</v>
       </c>
       <c r="AQ27" s="4">
         <v>150627</v>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="16"/>
-        <v>55101</v>
+        <v>55102</v>
       </c>
       <c r="AT27" s="7">
-        <v>117514</v>
+        <v>117515</v>
       </c>
       <c r="AU27" s="9">
         <f t="shared" si="17"/>
-        <v>0.78016557456498503</v>
+        <v>0.78017221348098287</v>
       </c>
       <c r="AV27" s="6">
         <v>152840</v>
@@ -4860,14 +4860,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>59009</v>
+        <v>59010</v>
       </c>
       <c r="AY27" s="7">
-        <v>118339</v>
+        <v>118340</v>
       </c>
       <c r="AZ27" s="9">
         <f t="shared" si="19"/>
-        <v>0.77426720753729394</v>
+        <v>0.77427375032713952</v>
       </c>
       <c r="BA27" s="6">
         <v>154902</v>
@@ -4877,14 +4877,14 @@
       </c>
       <c r="BC27" s="10">
         <f t="shared" si="20"/>
-        <v>46452</v>
+        <v>46453</v>
       </c>
       <c r="BD27" s="7">
-        <v>119499</v>
+        <v>119500</v>
       </c>
       <c r="BE27" s="9">
         <f t="shared" si="21"/>
-        <v>0.77144904520277335</v>
+        <v>0.7714555008973415</v>
       </c>
       <c r="BF27" s="6">
         <v>157244</v>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>73058</v>
+        <v>73059</v>
       </c>
       <c r="BI27" s="7">
-        <v>120361</v>
+        <v>120362</v>
       </c>
       <c r="BJ27" s="9">
         <f t="shared" si="23"/>
-        <v>0.76544097072066342</v>
+        <v>0.76544733026379386</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5038,14 +5038,14 @@
       </c>
       <c r="AN28" s="10">
         <f t="shared" si="14"/>
-        <v>129126</v>
+        <v>129127</v>
       </c>
       <c r="AO28" s="7">
-        <v>495484</v>
+        <v>495485</v>
       </c>
       <c r="AP28" s="9">
         <f t="shared" si="15"/>
-        <v>0.90047560459211951</v>
+        <v>0.90047742195777536</v>
       </c>
       <c r="AQ28" s="4">
         <v>558638</v>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="18"/>
-        <v>164923</v>
+        <v>164924</v>
       </c>
       <c r="AY28" s="7">
-        <v>508403</v>
+        <v>508404</v>
       </c>
       <c r="AZ28" s="9">
         <f t="shared" si="19"/>
-        <v>0.89474017665910499</v>
+        <v>0.89474193656252143</v>
       </c>
       <c r="BA28" s="6">
         <v>575661</v>
@@ -5106,14 +5106,14 @@
       </c>
       <c r="BH28" s="10">
         <f t="shared" si="22"/>
-        <v>208899</v>
+        <v>208900</v>
       </c>
       <c r="BI28" s="7">
-        <v>518271</v>
+        <v>518272</v>
       </c>
       <c r="BJ28" s="9">
         <f t="shared" si="23"/>
-        <v>0.8897066018447467</v>
+        <v>0.88970831852694932</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5343,14 +5343,14 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" si="0"/>
-        <v>90379</v>
+        <v>90381</v>
       </c>
       <c r="F30" s="7">
-        <v>165783</v>
+        <v>165785</v>
       </c>
       <c r="G30" s="9">
         <f t="shared" si="1"/>
-        <v>0.88863576670115085</v>
+        <v>0.88864648717027861</v>
       </c>
       <c r="H30" s="4">
         <v>195689</v>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="J30" s="10">
         <f t="shared" si="2"/>
-        <v>64632</v>
+        <v>64633</v>
       </c>
       <c r="K30" s="7">
-        <v>169922</v>
+        <v>169923</v>
       </c>
       <c r="L30" s="9">
         <f t="shared" si="3"/>
-        <v>0.86832678382535555</v>
+        <v>0.86833189397462296</v>
       </c>
       <c r="M30" s="4">
         <v>200801</v>
@@ -5377,14 +5377,14 @@
       </c>
       <c r="O30" s="10">
         <f t="shared" si="4"/>
-        <v>65236</v>
+        <v>65238</v>
       </c>
       <c r="P30" s="7">
-        <v>172943</v>
+        <v>172945</v>
       </c>
       <c r="Q30" s="9">
         <f t="shared" si="5"/>
-        <v>0.8612656311472553</v>
+        <v>0.86127559125701569</v>
       </c>
       <c r="R30" s="4">
         <v>205957</v>
@@ -5394,14 +5394,14 @@
       </c>
       <c r="T30" s="10">
         <f t="shared" si="6"/>
-        <v>50509</v>
+        <v>50510</v>
       </c>
       <c r="U30" s="7">
-        <v>176651</v>
+        <v>176652</v>
       </c>
       <c r="V30" s="9">
         <f t="shared" si="7"/>
-        <v>0.85770816238341008</v>
+        <v>0.8577130177658443</v>
       </c>
       <c r="W30" s="4">
         <v>211137</v>
@@ -5411,14 +5411,14 @@
       </c>
       <c r="Y30" s="10">
         <f t="shared" si="8"/>
-        <v>71110</v>
+        <v>71111</v>
       </c>
       <c r="Z30" s="7">
-        <v>180178</v>
+        <v>180179</v>
       </c>
       <c r="AA30" s="9">
         <f t="shared" si="9"/>
-        <v>0.85337008672094428</v>
+        <v>0.85337482298223433</v>
       </c>
       <c r="AB30" s="4">
         <v>214949</v>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="10"/>
-        <v>56771</v>
+        <v>56772</v>
       </c>
       <c r="AE30" s="7">
-        <v>183064</v>
+        <v>183065</v>
       </c>
       <c r="AF30" s="9">
         <f t="shared" si="11"/>
-        <v>0.85166248738072747</v>
+        <v>0.85166713964707907</v>
       </c>
       <c r="AG30" s="4">
         <v>218841</v>
@@ -5445,14 +5445,14 @@
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="12"/>
-        <v>65122</v>
+        <v>65123</v>
       </c>
       <c r="AJ30" s="7">
-        <v>186057</v>
+        <v>186058</v>
       </c>
       <c r="AK30" s="9">
         <f t="shared" si="13"/>
-        <v>0.85019260559036014</v>
+        <v>0.85019717511800807</v>
       </c>
       <c r="AL30" s="4">
         <v>222034</v>
@@ -5462,14 +5462,14 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="14"/>
-        <v>58876</v>
+        <v>58878</v>
       </c>
       <c r="AO30" s="7">
-        <v>185946</v>
+        <v>185948</v>
       </c>
       <c r="AP30" s="9">
         <f t="shared" si="15"/>
-        <v>0.83746633398488524</v>
+        <v>0.83747534161434734</v>
       </c>
       <c r="AQ30" s="4">
         <v>223141</v>
@@ -5479,14 +5479,14 @@
       </c>
       <c r="AS30" s="10">
         <f t="shared" si="16"/>
-        <v>61519</v>
+        <v>61520</v>
       </c>
       <c r="AT30" s="7">
-        <v>188421</v>
+        <v>188422</v>
       </c>
       <c r="AU30" s="9">
         <f t="shared" si="17"/>
-        <v>0.84440331449621542</v>
+        <v>0.84440779596757209</v>
       </c>
       <c r="AV30" s="6">
         <v>220757</v>
@@ -5496,14 +5496,14 @@
       </c>
       <c r="AX30" s="10">
         <f t="shared" si="18"/>
-        <v>71362</v>
+        <v>71363</v>
       </c>
       <c r="AY30" s="7">
-        <v>190719</v>
+        <v>190720</v>
       </c>
       <c r="AZ30" s="9">
         <f t="shared" si="19"/>
-        <v>0.86393183455111278</v>
+        <v>0.86393636441879529</v>
       </c>
       <c r="BA30" s="6">
         <v>218783</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="BC30" s="10">
         <f t="shared" si="20"/>
-        <v>49128</v>
+        <v>49132</v>
       </c>
       <c r="BD30" s="7">
-        <v>192489</v>
+        <v>192493</v>
       </c>
       <c r="BE30" s="9">
         <f t="shared" si="21"/>
-        <v>0.87981698760872651</v>
+        <v>0.87983527056489763</v>
       </c>
       <c r="BF30" s="6">
         <v>218115</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="BH30" s="10">
         <f t="shared" si="22"/>
-        <v>82460</v>
+        <v>82462</v>
       </c>
       <c r="BI30" s="7">
-        <v>193887</v>
+        <v>193889</v>
       </c>
       <c r="BJ30" s="9">
         <f t="shared" si="23"/>
-        <v>0.88892098205075309</v>
+        <v>0.88893015152557142</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5555,14 +5555,14 @@
       </c>
       <c r="E31" s="10">
         <f t="shared" si="0"/>
-        <v>60658</v>
+        <v>60660</v>
       </c>
       <c r="F31" s="7">
-        <v>86465</v>
+        <v>86467</v>
       </c>
       <c r="G31" s="9">
         <f t="shared" si="1"/>
-        <v>0.9165059040512179</v>
+        <v>0.9165271035169914</v>
       </c>
       <c r="H31" s="4">
         <v>98062</v>
@@ -5572,14 +5572,14 @@
       </c>
       <c r="J31" s="10">
         <f t="shared" si="2"/>
-        <v>38296</v>
+        <v>38297</v>
       </c>
       <c r="K31" s="7">
-        <v>87749</v>
+        <v>87750</v>
       </c>
       <c r="L31" s="9">
         <f t="shared" si="3"/>
-        <v>0.89483184108013303</v>
+        <v>0.89484203871020374</v>
       </c>
       <c r="M31" s="4">
         <v>98284</v>
@@ -5589,14 +5589,14 @@
       </c>
       <c r="O31" s="10">
         <f t="shared" si="4"/>
-        <v>38139</v>
+        <v>38140</v>
       </c>
       <c r="P31" s="7">
-        <v>89072</v>
+        <v>89073</v>
       </c>
       <c r="Q31" s="9">
         <f t="shared" si="5"/>
-        <v>0.9062716210166456</v>
+        <v>0.90628179561271416</v>
       </c>
       <c r="R31" s="4">
         <v>99303</v>
@@ -5606,14 +5606,14 @@
       </c>
       <c r="T31" s="10">
         <f t="shared" si="6"/>
-        <v>29638</v>
+        <v>29641</v>
       </c>
       <c r="U31" s="7">
-        <v>90335</v>
+        <v>90338</v>
       </c>
       <c r="V31" s="9">
         <f t="shared" si="7"/>
-        <v>0.90969054308530461</v>
+        <v>0.90972075365296112</v>
       </c>
       <c r="W31" s="4">
         <v>100790</v>
@@ -5623,14 +5623,14 @@
       </c>
       <c r="Y31" s="10">
         <f t="shared" si="8"/>
-        <v>40163</v>
+        <v>40164</v>
       </c>
       <c r="Z31" s="7">
-        <v>91467</v>
+        <v>91468</v>
       </c>
       <c r="AA31" s="9">
         <f t="shared" si="9"/>
-        <v>0.90750074412144066</v>
+        <v>0.90751066574064887</v>
       </c>
       <c r="AB31" s="4">
         <v>101382</v>
@@ -5640,14 +5640,14 @@
       </c>
       <c r="AD31" s="10">
         <f t="shared" si="10"/>
-        <v>32799</v>
+        <v>32800</v>
       </c>
       <c r="AE31" s="7">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="AF31" s="9">
         <f t="shared" si="11"/>
-        <v>0.91148330078317652</v>
+        <v>0.91149316446706519</v>
       </c>
       <c r="AG31" s="4">
         <v>101856</v>
@@ -5657,14 +5657,14 @@
       </c>
       <c r="AI31" s="10">
         <f t="shared" si="12"/>
-        <v>42303</v>
+        <v>42304</v>
       </c>
       <c r="AJ31" s="7">
-        <v>93492</v>
+        <v>93493</v>
       </c>
       <c r="AK31" s="9">
         <f t="shared" si="13"/>
-        <v>0.9178840716305372</v>
+        <v>0.91789388941250394</v>
       </c>
       <c r="AL31" s="4">
         <v>101556</v>
@@ -5674,14 +5674,14 @@
       </c>
       <c r="AN31" s="10">
         <f t="shared" si="14"/>
-        <v>35549</v>
+        <v>35550</v>
       </c>
       <c r="AO31" s="7">
-        <v>93147</v>
+        <v>93148</v>
       </c>
       <c r="AP31" s="9">
         <f t="shared" si="15"/>
-        <v>0.91719839300484463</v>
+        <v>0.91720823978888499</v>
       </c>
       <c r="AQ31" s="4">
         <v>101564</v>
@@ -5725,14 +5725,14 @@
       </c>
       <c r="BC31" s="10">
         <f t="shared" si="20"/>
-        <v>32842</v>
+        <v>32843</v>
       </c>
       <c r="BD31" s="7">
-        <v>95264</v>
+        <v>95265</v>
       </c>
       <c r="BE31" s="9">
         <f t="shared" si="21"/>
-        <v>0.94432053607716027</v>
+        <v>0.94433044874654293</v>
       </c>
       <c r="BF31" s="6">
         <v>102281</v>
@@ -5742,14 +5742,14 @@
       </c>
       <c r="BH31" s="10">
         <f t="shared" si="22"/>
-        <v>54732</v>
+        <v>54733</v>
       </c>
       <c r="BI31" s="7">
-        <v>95939</v>
+        <v>95940</v>
       </c>
       <c r="BJ31" s="9">
         <f t="shared" si="23"/>
-        <v>0.93799434890155553</v>
+        <v>0.9380041258884837</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5801,14 +5801,14 @@
       </c>
       <c r="O32" s="10">
         <f t="shared" si="4"/>
-        <v>100021</v>
+        <v>100022</v>
       </c>
       <c r="P32" s="7">
-        <v>296237</v>
+        <v>296238</v>
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="5"/>
-        <v>0.91940820101550569</v>
+        <v>0.91941130463929688</v>
       </c>
       <c r="R32" s="4">
         <v>325000</v>
@@ -5818,14 +5818,14 @@
       </c>
       <c r="T32" s="10">
         <f t="shared" si="6"/>
-        <v>76112</v>
+        <v>76113</v>
       </c>
       <c r="U32" s="7">
-        <v>300157</v>
+        <v>300158</v>
       </c>
       <c r="V32" s="9">
         <f t="shared" si="7"/>
-        <v>0.92356000000000005</v>
+        <v>0.92356307692307693</v>
       </c>
       <c r="W32" s="4">
         <v>327986</v>
@@ -5886,14 +5886,14 @@
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="14"/>
-        <v>93775</v>
+        <v>93778</v>
       </c>
       <c r="AO32" s="7">
-        <v>311833</v>
+        <v>311836</v>
       </c>
       <c r="AP32" s="9">
         <f t="shared" si="15"/>
-        <v>0.93250100925524437</v>
+        <v>0.93250998041297228</v>
       </c>
       <c r="AQ32" s="4">
         <v>335747</v>
@@ -5903,14 +5903,14 @@
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="16"/>
-        <v>98663</v>
+        <v>98666</v>
       </c>
       <c r="AT32" s="7">
-        <v>314702</v>
+        <v>314705</v>
       </c>
       <c r="AU32" s="9">
         <f t="shared" si="17"/>
-        <v>0.93731887403312608</v>
+        <v>0.9373278093326225</v>
       </c>
       <c r="AV32" s="6">
         <v>338656</v>
@@ -5920,14 +5920,14 @@
       </c>
       <c r="AX32" s="10">
         <f t="shared" si="18"/>
-        <v>118619</v>
+        <v>118621</v>
       </c>
       <c r="AY32" s="7">
-        <v>318037</v>
+        <v>318039</v>
       </c>
       <c r="AZ32" s="9">
         <f t="shared" si="19"/>
-        <v>0.93911520835301898</v>
+        <v>0.9391211140508362</v>
       </c>
       <c r="BA32" s="6">
         <v>341978</v>
@@ -5937,14 +5937,14 @@
       </c>
       <c r="BC32" s="10">
         <f t="shared" si="20"/>
-        <v>78494</v>
+        <v>78497</v>
       </c>
       <c r="BD32" s="7">
-        <v>320893</v>
+        <v>320896</v>
       </c>
       <c r="BE32" s="9">
         <f t="shared" si="21"/>
-        <v>0.93834398704010202</v>
+        <v>0.93835275953423902</v>
       </c>
       <c r="BF32" s="6">
         <v>346732</v>
@@ -5954,14 +5954,14 @@
       </c>
       <c r="BH32" s="10">
         <f t="shared" si="22"/>
-        <v>160619</v>
+        <v>160621</v>
       </c>
       <c r="BI32" s="7">
-        <v>323996</v>
+        <v>323998</v>
       </c>
       <c r="BJ32" s="9">
         <f t="shared" si="23"/>
-        <v>0.93442774246392024</v>
+        <v>0.93443351060761626</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5979,14 +5979,14 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="0"/>
-        <v>401551</v>
+        <v>401552</v>
       </c>
       <c r="F33" s="7">
-        <v>722979</v>
+        <v>722980</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="1"/>
-        <v>0.94659627870803531</v>
+        <v>0.94659758800786109</v>
       </c>
       <c r="H33" s="4">
         <v>790674</v>
@@ -5996,14 +5996,14 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v>169976</v>
+        <v>169977</v>
       </c>
       <c r="K33" s="7">
-        <v>735194</v>
+        <v>735195</v>
       </c>
       <c r="L33" s="9">
         <f t="shared" si="3"/>
-        <v>0.92983201673508931</v>
+        <v>0.92983328147883959</v>
       </c>
       <c r="M33" s="4">
         <v>801034</v>
@@ -6013,14 +6013,14 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="4"/>
-        <v>180419</v>
+        <v>180420</v>
       </c>
       <c r="P33" s="7">
-        <v>744296</v>
+        <v>744297</v>
       </c>
       <c r="Q33" s="9">
         <f t="shared" si="5"/>
-        <v>0.92916904900416208</v>
+        <v>0.92917029739062262</v>
       </c>
       <c r="R33" s="4">
         <v>811485</v>
@@ -6030,14 +6030,14 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="6"/>
-        <v>138451</v>
+        <v>138452</v>
       </c>
       <c r="U33" s="7">
-        <v>751888</v>
+        <v>751889</v>
       </c>
       <c r="V33" s="9">
         <f t="shared" si="7"/>
-        <v>0.92655810027295638</v>
+        <v>0.92655933258162504</v>
       </c>
       <c r="W33" s="4">
         <v>819064</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>204479</v>
+        <v>204480</v>
       </c>
       <c r="Z33" s="7">
-        <v>761130</v>
+        <v>761131</v>
       </c>
       <c r="AA33" s="9">
         <f t="shared" si="9"/>
-        <v>0.92926804254612583</v>
+        <v>0.92926926345194028</v>
       </c>
       <c r="AB33" s="4">
         <v>823883</v>
@@ -6064,14 +6064,14 @@
       </c>
       <c r="AD33" s="10">
         <f t="shared" si="10"/>
-        <v>153441</v>
+        <v>153442</v>
       </c>
       <c r="AE33" s="7">
-        <v>767917</v>
+        <v>767918</v>
       </c>
       <c r="AF33" s="9">
         <f t="shared" si="11"/>
-        <v>0.93207045175103742</v>
+        <v>0.93207166551561327</v>
       </c>
       <c r="AG33" s="4">
         <v>827687</v>
@@ -6081,14 +6081,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>226200</v>
+        <v>226201</v>
       </c>
       <c r="AJ33" s="7">
-        <v>773750</v>
+        <v>773751</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="13"/>
-        <v>0.93483406166823935</v>
+        <v>0.93483526985442567</v>
       </c>
       <c r="AL33" s="4">
         <v>833066</v>
@@ -6098,14 +6098,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>170644</v>
+        <v>170645</v>
       </c>
       <c r="AO33" s="7">
-        <v>774383</v>
+        <v>774384</v>
       </c>
       <c r="AP33" s="9">
         <f t="shared" si="15"/>
-        <v>0.92955780214292749</v>
+        <v>0.92955900252801094</v>
       </c>
       <c r="AQ33" s="4">
         <v>838229</v>
@@ -6115,14 +6115,14 @@
       </c>
       <c r="AS33" s="10">
         <f t="shared" si="16"/>
-        <v>188058</v>
+        <v>188060</v>
       </c>
       <c r="AT33" s="7">
-        <v>782814</v>
+        <v>782816</v>
       </c>
       <c r="AU33" s="9">
         <f t="shared" si="17"/>
-        <v>0.93389038079092945</v>
+        <v>0.93389276677375754</v>
       </c>
       <c r="AV33" s="6">
         <v>846900</v>
@@ -6132,14 +6132,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>217576</v>
+        <v>217579</v>
       </c>
       <c r="AY33" s="7">
-        <v>788684</v>
+        <v>788687</v>
       </c>
       <c r="AZ33" s="9">
         <f t="shared" si="19"/>
-        <v>0.93125988900696655</v>
+        <v>0.9312634313378203</v>
       </c>
       <c r="BA33" s="6">
         <v>854421</v>
@@ -6149,14 +6149,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>134192</v>
+        <v>134194</v>
       </c>
       <c r="BD33" s="7">
-        <v>795539</v>
+        <v>795541</v>
       </c>
       <c r="BE33" s="9">
         <f t="shared" si="21"/>
-        <v>0.93108549532373386</v>
+        <v>0.93108783609017098</v>
       </c>
       <c r="BF33" s="6">
         <v>864165</v>
@@ -6166,14 +6166,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>281121</v>
+        <v>281123</v>
       </c>
       <c r="BI33" s="7">
-        <v>802662</v>
+        <v>802664</v>
       </c>
       <c r="BJ33" s="9">
         <f t="shared" si="23"/>
-        <v>0.92882956379858017</v>
+        <v>0.92883187817141399</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6615,14 +6615,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>635198</v>
+        <v>635201</v>
       </c>
       <c r="F36" s="7">
-        <v>1117299</v>
+        <v>1117302</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="1"/>
-        <v>0.9062115247044854</v>
+        <v>0.90621395792475512</v>
       </c>
       <c r="H36" s="4">
         <v>1268548</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>364146</v>
+        <v>364149</v>
       </c>
       <c r="K36" s="7">
-        <v>1135864</v>
+        <v>1135867</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="3"/>
-        <v>0.89540482504406615</v>
+        <v>0.89540718995260726</v>
       </c>
       <c r="M36" s="4">
         <v>1291465</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>366225</v>
+        <v>366227</v>
       </c>
       <c r="P36" s="7">
-        <v>1150167</v>
+        <v>1150169</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="5"/>
-        <v>0.89059091806591739</v>
+        <v>0.89059246669480008</v>
       </c>
       <c r="R36" s="4">
         <v>1304709</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>303563</v>
+        <v>303565</v>
       </c>
       <c r="U36" s="7">
-        <v>1161620</v>
+        <v>1161622</v>
       </c>
       <c r="V36" s="9">
         <f t="shared" si="7"/>
-        <v>0.89032880128825664</v>
+        <v>0.89033033419712748</v>
       </c>
       <c r="W36" s="4">
         <v>1322652</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>444957</v>
+        <v>444960</v>
       </c>
       <c r="Z36" s="7">
-        <v>1173310</v>
+        <v>1173313</v>
       </c>
       <c r="AA36" s="9">
         <f t="shared" si="9"/>
-        <v>0.8870889697365596</v>
+        <v>0.88709123790687194</v>
       </c>
       <c r="AB36" s="4">
         <v>1322160</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>336119</v>
+        <v>336122</v>
       </c>
       <c r="AE36" s="7">
-        <v>1183570</v>
+        <v>1183573</v>
       </c>
       <c r="AF36" s="9">
         <f t="shared" si="11"/>
-        <v>0.89517910086525077</v>
+        <v>0.89518136987959096</v>
       </c>
       <c r="AG36" s="4">
         <v>1336822</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>409282</v>
+        <v>409285</v>
       </c>
       <c r="AJ36" s="7">
-        <v>1192842</v>
+        <v>1192845</v>
       </c>
       <c r="AK36" s="9">
         <f t="shared" si="13"/>
-        <v>0.89229680540864831</v>
+        <v>0.89229904953688677</v>
       </c>
       <c r="AL36" s="4">
         <v>1349209</v>
@@ -6734,14 +6734,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>349939</v>
+        <v>349942</v>
       </c>
       <c r="AO36" s="7">
-        <v>1189347</v>
+        <v>1189350</v>
       </c>
       <c r="AP36" s="9">
         <f t="shared" si="15"/>
-        <v>0.88151427984841491</v>
+        <v>0.8815165033734581</v>
       </c>
       <c r="AQ36" s="4">
         <v>1349417</v>
@@ -6751,14 +6751,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>371127</v>
+        <v>371130</v>
       </c>
       <c r="AT36" s="7">
-        <v>1201601</v>
+        <v>1201604</v>
       </c>
       <c r="AU36" s="9">
         <f t="shared" si="17"/>
-        <v>0.89045936133900794</v>
+        <v>0.89046158452131552</v>
       </c>
       <c r="AV36" s="6">
         <v>1347780</v>
@@ -6768,14 +6768,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>460660</v>
+        <v>460662</v>
       </c>
       <c r="AY36" s="7">
-        <v>1211603</v>
+        <v>1211605</v>
       </c>
       <c r="AZ36" s="9">
         <f t="shared" si="19"/>
-        <v>0.89896199676505073</v>
+        <v>0.89896348068675902</v>
       </c>
       <c r="BA36" s="6">
         <v>1364152</v>
@@ -6785,14 +6785,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>293542</v>
+        <v>293544</v>
       </c>
       <c r="BD36" s="7">
-        <v>1221217</v>
+        <v>1221219</v>
       </c>
       <c r="BE36" s="9">
         <f t="shared" si="21"/>
-        <v>0.89522062057600615</v>
+        <v>0.89522208668828696</v>
       </c>
       <c r="BF36" s="6">
         <v>1384075</v>
@@ -6802,14 +6802,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="22"/>
-        <v>511475</v>
+        <v>511477</v>
       </c>
       <c r="BI36" s="7">
-        <v>1229537</v>
+        <v>1229539</v>
       </c>
       <c r="BJ36" s="9">
         <f t="shared" si="23"/>
-        <v>0.8883456460090674</v>
+        <v>0.88834709101746656</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6878,14 +6878,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>133639</v>
+        <v>133640</v>
       </c>
       <c r="U37" s="7">
-        <v>578190</v>
+        <v>578191</v>
       </c>
       <c r="V37" s="9">
         <f t="shared" si="7"/>
-        <v>0.87121811417644957</v>
+        <v>0.87121962097890926</v>
       </c>
       <c r="W37" s="4">
         <v>677316</v>
@@ -6895,14 +6895,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>185287</v>
+        <v>185289</v>
       </c>
       <c r="Z37" s="7">
-        <v>587375</v>
+        <v>587377</v>
       </c>
       <c r="AA37" s="9">
         <f t="shared" si="9"/>
-        <v>0.86720969237401746</v>
+        <v>0.86721264520548758</v>
       </c>
       <c r="AB37" s="4">
         <v>682420</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>163059</v>
+        <v>163061</v>
       </c>
       <c r="AO37" s="7">
-        <v>603938</v>
+        <v>603940</v>
       </c>
       <c r="AP37" s="9">
         <f t="shared" si="15"/>
-        <v>0.86483057461289847</v>
+        <v>0.86483343858428163</v>
       </c>
       <c r="AQ37" s="4">
         <v>700400</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>175157</v>
+        <v>175159</v>
       </c>
       <c r="AT37" s="7">
-        <v>611986</v>
+        <v>611988</v>
       </c>
       <c r="AU37" s="9">
         <f t="shared" si="17"/>
-        <v>0.87376641918903486</v>
+        <v>0.87376927470017129</v>
       </c>
       <c r="AV37" s="6">
         <v>698615</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>123318</v>
+        <v>123319</v>
       </c>
       <c r="BD37" s="7">
-        <v>626354</v>
+        <v>626355</v>
       </c>
       <c r="BE37" s="9">
         <f t="shared" si="21"/>
-        <v>0.89326776897691651</v>
+        <v>0.89326919511575964</v>
       </c>
       <c r="BF37" s="6">
         <v>706472</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="22"/>
-        <v>257257</v>
+        <v>257258</v>
       </c>
       <c r="BI37" s="7">
-        <v>632156</v>
+        <v>632157</v>
       </c>
       <c r="BJ37" s="9">
         <f t="shared" si="23"/>
-        <v>0.89480687132681835</v>
+        <v>0.89480828681108382</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7650,14 +7650,14 @@
       </c>
       <c r="BH40" s="10">
         <f t="shared" si="22"/>
-        <v>136545</v>
+        <v>136549</v>
       </c>
       <c r="BI40" s="7">
-        <v>267297</v>
+        <v>267301</v>
       </c>
       <c r="BJ40" s="9">
         <f t="shared" si="23"/>
-        <v>0.91793443546226916</v>
+        <v>0.91794817200903867</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>385824</v>
+        <v>385851</v>
       </c>
       <c r="F41" s="7">
-        <v>690910</v>
+        <v>690937</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="1"/>
-        <v>0.85036123521520268</v>
+        <v>0.85039446639343252</v>
       </c>
       <c r="H41" s="4">
         <v>835051</v>
@@ -7692,14 +7692,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>211117</v>
+        <v>211143</v>
       </c>
       <c r="K41" s="7">
-        <v>701637</v>
+        <v>701663</v>
       </c>
       <c r="L41" s="9">
         <f t="shared" si="3"/>
-        <v>0.84023251274473054</v>
+        <v>0.84026364856757252</v>
       </c>
       <c r="M41" s="4">
         <v>852643</v>
@@ -7709,14 +7709,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>211028</v>
+        <v>211053</v>
       </c>
       <c r="P41" s="7">
-        <v>709898</v>
+        <v>709923</v>
       </c>
       <c r="Q41" s="9">
         <f t="shared" si="5"/>
-        <v>0.83258526722203785</v>
+        <v>0.83261458781694098</v>
       </c>
       <c r="R41" s="4">
         <v>868359</v>
@@ -7726,14 +7726,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171898</v>
+        <v>171927</v>
       </c>
       <c r="U41" s="7">
-        <v>719445</v>
+        <v>719474</v>
       </c>
       <c r="V41" s="9">
         <f t="shared" si="7"/>
-        <v>0.82851101906008917</v>
+        <v>0.82854441538580237</v>
       </c>
       <c r="W41" s="4">
         <v>879806</v>
@@ -7743,14 +7743,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>230027</v>
+        <v>230058</v>
       </c>
       <c r="Z41" s="7">
-        <v>727686</v>
+        <v>727717</v>
       </c>
       <c r="AA41" s="9">
         <f t="shared" si="9"/>
-        <v>0.82709824665892251</v>
+        <v>0.82713348169937462</v>
       </c>
       <c r="AB41" s="4">
         <v>882248</v>
@@ -7760,14 +7760,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>187377</v>
+        <v>187410</v>
       </c>
       <c r="AE41" s="7">
-        <v>735440</v>
+        <v>735473</v>
       </c>
       <c r="AF41" s="9">
         <f t="shared" si="11"/>
-        <v>0.83359780923277804</v>
+        <v>0.8336352136814138</v>
       </c>
       <c r="AG41" s="4">
         <v>877145</v>
@@ -7777,14 +7777,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>242379</v>
+        <v>242416</v>
       </c>
       <c r="AJ41" s="7">
-        <v>743241</v>
+        <v>743278</v>
       </c>
       <c r="AK41" s="9">
         <f t="shared" si="13"/>
-        <v>0.84734108955759879</v>
+        <v>0.84738327186497098</v>
       </c>
       <c r="AL41" s="4">
         <v>875890</v>
@@ -7794,14 +7794,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>205196</v>
+        <v>205241</v>
       </c>
       <c r="AO41" s="7">
-        <v>742041</v>
+        <v>742086</v>
       </c>
       <c r="AP41" s="9">
         <f t="shared" si="15"/>
-        <v>0.84718514882005735</v>
+        <v>0.8472365251344347</v>
       </c>
       <c r="AQ41" s="4">
         <v>865402</v>
@@ -7811,14 +7811,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>247841</v>
+        <v>247883</v>
       </c>
       <c r="AT41" s="7">
-        <v>748309</v>
+        <v>748351</v>
       </c>
       <c r="AU41" s="9">
         <f t="shared" si="17"/>
-        <v>0.86469525145539294</v>
+        <v>0.86474378381376515</v>
       </c>
       <c r="AV41" s="6">
         <v>863602</v>
@@ -7828,14 +7828,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>252882</v>
+        <v>252922</v>
       </c>
       <c r="AY41" s="7">
-        <v>753160</v>
+        <v>753200</v>
       </c>
       <c r="AZ41" s="9">
         <f t="shared" si="19"/>
-        <v>0.87211470098494448</v>
+        <v>0.87216101861737239</v>
       </c>
       <c r="BA41" s="6">
         <v>853803</v>
@@ -7845,14 +7845,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>156217</v>
+        <v>156258</v>
       </c>
       <c r="BD41" s="7">
-        <v>759954</v>
+        <v>759995</v>
       </c>
       <c r="BE41" s="9">
         <f t="shared" si="21"/>
-        <v>0.89008120140126001</v>
+        <v>0.89012922184625731</v>
       </c>
       <c r="BF41" s="6">
         <v>867754</v>
@@ -7862,14 +7862,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="22"/>
-        <v>339076</v>
+        <v>339120</v>
       </c>
       <c r="BI41" s="7">
-        <v>767222</v>
+        <v>767266</v>
       </c>
       <c r="BJ41" s="9">
         <f t="shared" si="23"/>
-        <v>0.88414688955625675</v>
+        <v>0.88419759517098162</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8311,14 +8311,14 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" si="0"/>
-        <v>145439</v>
+        <v>145441</v>
       </c>
       <c r="F44" s="7">
-        <v>238311</v>
+        <v>238313</v>
       </c>
       <c r="G44" s="9">
         <f t="shared" si="1"/>
-        <v>0.89750194895434365</v>
+        <v>0.89750948114504359</v>
       </c>
       <c r="H44" s="4">
         <v>275203</v>
@@ -8328,14 +8328,14 @@
       </c>
       <c r="J44" s="10">
         <f t="shared" si="2"/>
-        <v>93151</v>
+        <v>93153</v>
       </c>
       <c r="K44" s="7">
-        <v>243340</v>
+        <v>243342</v>
       </c>
       <c r="L44" s="9">
         <f t="shared" si="3"/>
-        <v>0.88422001213649559</v>
+        <v>0.88422727949913338</v>
       </c>
       <c r="M44" s="4">
         <v>282140</v>
@@ -8345,14 +8345,14 @@
       </c>
       <c r="O44" s="10">
         <f t="shared" si="4"/>
-        <v>95389</v>
+        <v>95391</v>
       </c>
       <c r="P44" s="7">
-        <v>247657</v>
+        <v>247659</v>
       </c>
       <c r="Q44" s="9">
         <f t="shared" si="5"/>
-        <v>0.87778053448642512</v>
+        <v>0.87778762316580417</v>
       </c>
       <c r="R44" s="4">
         <v>288291</v>
@@ -8362,14 +8362,14 @@
       </c>
       <c r="T44" s="10">
         <f t="shared" si="6"/>
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="U44" s="7">
-        <v>252384</v>
+        <v>252386</v>
       </c>
       <c r="V44" s="9">
         <f t="shared" si="7"/>
-        <v>0.87544876531005134</v>
+        <v>0.875455702744796</v>
       </c>
       <c r="W44" s="4">
         <v>293969</v>
@@ -8379,14 +8379,14 @@
       </c>
       <c r="Y44" s="10">
         <f t="shared" si="8"/>
-        <v>112586</v>
+        <v>112588</v>
       </c>
       <c r="Z44" s="7">
-        <v>256639</v>
+        <v>256641</v>
       </c>
       <c r="AA44" s="9">
         <f t="shared" si="9"/>
-        <v>0.87301382118522697</v>
+        <v>0.87302062462368479</v>
       </c>
       <c r="AB44" s="4">
         <v>298180</v>
@@ -8396,14 +8396,14 @@
       </c>
       <c r="AD44" s="10">
         <f t="shared" si="10"/>
-        <v>90076</v>
+        <v>90078</v>
       </c>
       <c r="AE44" s="7">
-        <v>260443</v>
+        <v>260445</v>
       </c>
       <c r="AF44" s="9">
         <f t="shared" si="11"/>
-        <v>0.87344221611107387</v>
+        <v>0.87344892346904557</v>
       </c>
       <c r="AG44" s="4">
         <v>302892</v>
@@ -8413,14 +8413,14 @@
       </c>
       <c r="AI44" s="10">
         <f t="shared" si="12"/>
-        <v>102640</v>
+        <v>102642</v>
       </c>
       <c r="AJ44" s="7">
-        <v>264189</v>
+        <v>264191</v>
       </c>
       <c r="AK44" s="9">
         <f t="shared" si="13"/>
-        <v>0.87222178202131451</v>
+        <v>0.87222838503492994</v>
       </c>
       <c r="AL44" s="4">
         <v>305036</v>
@@ -8430,14 +8430,14 @@
       </c>
       <c r="AN44" s="10">
         <f t="shared" si="14"/>
-        <v>90728</v>
+        <v>90730</v>
       </c>
       <c r="AO44" s="7">
-        <v>264393</v>
+        <v>264395</v>
       </c>
       <c r="AP44" s="9">
         <f t="shared" si="15"/>
-        <v>0.86675998898490669</v>
+        <v>0.86676654558806177</v>
       </c>
       <c r="AQ44" s="4">
         <v>305678</v>
@@ -8447,14 +8447,14 @@
       </c>
       <c r="AS44" s="10">
         <f t="shared" si="16"/>
-        <v>97405</v>
+        <v>97407</v>
       </c>
       <c r="AT44" s="7">
-        <v>267056</v>
+        <v>267058</v>
       </c>
       <c r="AU44" s="9">
         <f t="shared" si="17"/>
-        <v>0.87365135861920062</v>
+        <v>0.87365790145185451</v>
       </c>
       <c r="AV44" s="6">
         <v>308055</v>
@@ -8464,14 +8464,14 @@
       </c>
       <c r="AX44" s="10">
         <f t="shared" si="18"/>
-        <v>107805</v>
+        <v>107807</v>
       </c>
       <c r="AY44" s="7">
-        <v>269509</v>
+        <v>269511</v>
       </c>
       <c r="AZ44" s="9">
         <f t="shared" si="19"/>
-        <v>0.8748729934589603</v>
+        <v>0.87487948580610608</v>
       </c>
       <c r="BA44" s="6">
         <v>313476</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="BC44" s="10">
         <f t="shared" si="20"/>
-        <v>73471</v>
+        <v>73474</v>
       </c>
       <c r="BD44" s="7">
-        <v>272816</v>
+        <v>272819</v>
       </c>
       <c r="BE44" s="9">
         <f t="shared" si="21"/>
-        <v>0.87029310058824283</v>
+        <v>0.87030267069887324</v>
       </c>
       <c r="BF44" s="6">
         <v>319463</v>
@@ -8498,14 +8498,14 @@
       </c>
       <c r="BH44" s="10">
         <f t="shared" si="22"/>
-        <v>129335</v>
+        <v>129339</v>
       </c>
       <c r="BI44" s="7">
-        <v>275761</v>
+        <v>275765</v>
       </c>
       <c r="BJ44" s="9">
         <f t="shared" si="23"/>
-        <v>0.86320168532819141</v>
+        <v>0.86321420634001433</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8523,14 +8523,14 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" si="0"/>
-        <v>119235</v>
+        <v>119237</v>
       </c>
       <c r="F45" s="7">
-        <v>212494</v>
+        <v>212496</v>
       </c>
       <c r="G45" s="9">
         <f t="shared" si="1"/>
-        <v>0.88522568685038217</v>
+        <v>0.88523401862150841</v>
       </c>
       <c r="H45" s="4">
         <v>247611</v>
@@ -8540,14 +8540,14 @@
       </c>
       <c r="J45" s="10">
         <f t="shared" si="2"/>
-        <v>65568</v>
+        <v>65572</v>
       </c>
       <c r="K45" s="7">
-        <v>215859</v>
+        <v>215863</v>
       </c>
       <c r="L45" s="9">
         <f t="shared" si="3"/>
-        <v>0.87176660164532271</v>
+        <v>0.87178275601649358</v>
       </c>
       <c r="M45" s="4">
         <v>252576</v>
@@ -8557,14 +8557,14 @@
       </c>
       <c r="O45" s="10">
         <f t="shared" si="4"/>
-        <v>66781</v>
+        <v>66784</v>
       </c>
       <c r="P45" s="7">
-        <v>218603</v>
+        <v>218606</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="5"/>
-        <v>0.8654939503357405</v>
+        <v>0.86550582794881536</v>
       </c>
       <c r="R45" s="4">
         <v>256692</v>
@@ -8574,14 +8574,14 @@
       </c>
       <c r="T45" s="10">
         <f t="shared" si="6"/>
-        <v>50477</v>
+        <v>50480</v>
       </c>
       <c r="U45" s="7">
-        <v>221883</v>
+        <v>221886</v>
       </c>
       <c r="V45" s="9">
         <f t="shared" si="7"/>
-        <v>0.86439390397830862</v>
+        <v>0.86440559113645921</v>
       </c>
       <c r="W45" s="4">
         <v>257705</v>
@@ -8591,14 +8591,14 @@
       </c>
       <c r="Y45" s="10">
         <f t="shared" si="8"/>
-        <v>78578</v>
+        <v>78581</v>
       </c>
       <c r="Z45" s="7">
-        <v>225469</v>
+        <v>225472</v>
       </c>
       <c r="AA45" s="9">
         <f t="shared" si="9"/>
-        <v>0.87491123571525586</v>
+        <v>0.87492287693292714</v>
       </c>
       <c r="AB45" s="4">
         <v>256988</v>
@@ -8608,14 +8608,14 @@
       </c>
       <c r="AD45" s="10">
         <f t="shared" si="10"/>
-        <v>67745</v>
+        <v>67749</v>
       </c>
       <c r="AE45" s="7">
-        <v>228437</v>
+        <v>228441</v>
       </c>
       <c r="AF45" s="9">
         <f t="shared" si="11"/>
-        <v>0.88890142730399868</v>
+        <v>0.88891699223310039</v>
       </c>
       <c r="AG45" s="4">
         <v>259488</v>
@@ -8625,14 +8625,14 @@
       </c>
       <c r="AI45" s="10">
         <f t="shared" si="12"/>
-        <v>74814</v>
+        <v>74819</v>
       </c>
       <c r="AJ45" s="7">
-        <v>232243</v>
+        <v>232248</v>
       </c>
       <c r="AK45" s="9">
         <f t="shared" si="13"/>
-        <v>0.89500477864101613</v>
+        <v>0.89502404735479102</v>
       </c>
       <c r="AL45" s="4">
         <v>264815</v>
@@ -8642,14 +8642,14 @@
       </c>
       <c r="AN45" s="10">
         <f t="shared" si="14"/>
-        <v>67519</v>
+        <v>67524</v>
       </c>
       <c r="AO45" s="7">
-        <v>234539</v>
+        <v>234544</v>
       </c>
       <c r="AP45" s="9">
         <f t="shared" si="15"/>
-        <v>0.8856711289013085</v>
+        <v>0.88569001000698599</v>
       </c>
       <c r="AQ45" s="4">
         <v>268317</v>
@@ -8659,14 +8659,14 @@
       </c>
       <c r="AS45" s="10">
         <f t="shared" si="16"/>
-        <v>78035</v>
+        <v>78039</v>
       </c>
       <c r="AT45" s="7">
-        <v>237915</v>
+        <v>237919</v>
       </c>
       <c r="AU45" s="9">
         <f t="shared" si="17"/>
-        <v>0.88669372421426895</v>
+        <v>0.88670863195399474</v>
       </c>
       <c r="AV45" s="6">
         <v>271955</v>
@@ -8676,14 +8676,14 @@
       </c>
       <c r="AX45" s="10">
         <f t="shared" si="18"/>
-        <v>83970</v>
+        <v>83976</v>
       </c>
       <c r="AY45" s="7">
-        <v>240119</v>
+        <v>240125</v>
       </c>
       <c r="AZ45" s="9">
         <f t="shared" si="19"/>
-        <v>0.88293651523229943</v>
+        <v>0.8829585777058705</v>
       </c>
       <c r="BA45" s="6">
         <v>276045</v>
@@ -8693,14 +8693,14 @@
       </c>
       <c r="BC45" s="10">
         <f t="shared" si="20"/>
-        <v>53655</v>
+        <v>53661</v>
       </c>
       <c r="BD45" s="7">
-        <v>242833</v>
+        <v>242839</v>
       </c>
       <c r="BE45" s="9">
         <f t="shared" si="21"/>
-        <v>0.87968628303356333</v>
+        <v>0.87970801862015247</v>
       </c>
       <c r="BF45" s="6">
         <v>279089</v>
@@ -8710,14 +8710,14 @@
       </c>
       <c r="BH45" s="10">
         <f t="shared" si="22"/>
-        <v>114247</v>
+        <v>114253</v>
       </c>
       <c r="BI45" s="7">
-        <v>245085</v>
+        <v>245091</v>
       </c>
       <c r="BJ45" s="9">
         <f t="shared" si="23"/>
-        <v>0.87816073008968465</v>
+        <v>0.87818222860807837</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9121,10 +9121,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="24"/>
+      <c r="B48" s="21"/>
       <c r="C48" s="13">
         <f>SUM(C10:C47)</f>
         <v>8817798</v>
@@ -9135,15 +9135,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>4591805</v>
+        <v>4591851</v>
       </c>
       <c r="F48" s="13">
         <f>SUM(F10:F47)</f>
-        <v>8024123</v>
+        <v>8024169</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.90999170087588765</v>
+        <v>0.90999691759779477</v>
       </c>
       <c r="H48" s="13">
         <f>SUM(H10:H47)</f>
@@ -9155,15 +9155,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>2452735</v>
+        <v>2452776</v>
       </c>
       <c r="K48" s="13">
         <f>SUM(K10:K47)</f>
-        <v>8179175</v>
+        <v>8179216</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.89661235987511501</v>
+        <v>0.89661685435123939</v>
       </c>
       <c r="M48" s="13">
         <f>SUM(M10:M47)</f>
@@ -9175,15 +9175,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2507148</v>
+        <v>2507189</v>
       </c>
       <c r="P48" s="13">
         <f>SUM(P10:P47)</f>
-        <v>8297471</v>
+        <v>8297512</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.89060097394895843</v>
+        <v>0.89060537464405354</v>
       </c>
       <c r="R48" s="13">
         <f>SUM(R10:R47)</f>
@@ -9195,15 +9195,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>2026610</v>
+        <v>2026658</v>
       </c>
       <c r="U48" s="13">
         <f>SUM(U10:U47)</f>
-        <v>8410260</v>
+        <v>8410308</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.88806859183285147</v>
+        <v>0.88807366031972435</v>
       </c>
       <c r="W48" s="13">
         <f>SUM(W10:W47)</f>
@@ -9215,15 +9215,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>2872071</v>
+        <v>2872121</v>
       </c>
       <c r="Z48" s="13">
         <f>SUM(Z10:Z47)</f>
-        <v>8522311</v>
+        <v>8522361</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.88633063252598232</v>
+        <v>0.88633583258634463</v>
       </c>
       <c r="AB48" s="13">
         <f>SUM(AB10:AB47)</f>
@@ -9235,15 +9235,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2247946</v>
+        <v>2247995</v>
       </c>
       <c r="AE48" s="13">
         <f>SUM(AE10:AE47)</f>
-        <v>8617200</v>
+        <v>8617249</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.8923047260195176</v>
+        <v>0.89230979993350068</v>
       </c>
       <c r="AG48" s="13">
         <f>SUM(AG10:AG47)</f>
@@ -9255,15 +9255,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2832520</v>
+        <v>2832573</v>
       </c>
       <c r="AJ48" s="13">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8715185</v>
+        <v>8715238</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.89316305623969017</v>
+        <v>0.89316848786758796</v>
       </c>
       <c r="AL48" s="13">
         <f>SUM(AL10:AL47)</f>
@@ -9275,15 +9275,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2422600</v>
+        <v>2422672</v>
       </c>
       <c r="AO48" s="13">
         <f>SUM(AO10:AO47)</f>
-        <v>8712961</v>
+        <v>8713033</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.88486596195963196</v>
+        <v>0.88487327409488203</v>
       </c>
       <c r="AQ48" s="13">
         <f>SUM(AQ10:AQ47)</f>
@@ -9295,15 +9295,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>2606985</v>
+        <v>2607052</v>
       </c>
       <c r="AT48" s="13">
         <f>SUM(AT10:AT47)</f>
-        <v>8806441</v>
+        <v>8806508</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.88936009574634289</v>
+        <v>0.88936686205822924</v>
       </c>
       <c r="AV48" s="13">
         <f>SUM(AV10:AV47)</f>
@@ -9315,15 +9315,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>3160673</v>
+        <v>3160738</v>
       </c>
       <c r="AY48" s="13">
         <f>SUM(AY10:AY47)</f>
-        <v>8886674</v>
+        <v>8886739</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.89110555390604229</v>
+        <v>0.89111207173948637</v>
       </c>
       <c r="BA48" s="13">
         <f>SUM(BA10:BA47)</f>
@@ -9335,15 +9335,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2003659</v>
+        <v>2003733</v>
       </c>
       <c r="BD48" s="13">
         <f>SUM(BD10:BD47)</f>
-        <v>8966913</v>
+        <v>8966987</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.8918500702635882</v>
+        <v>0.89185743031104259</v>
       </c>
       <c r="BF48" s="13">
         <f>SUM(BF10:BF47)</f>
@@ -9355,15 +9355,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>3828482</v>
+        <v>3828566</v>
       </c>
       <c r="BI48" s="13">
         <f>SUM(BI10:BI47)</f>
-        <v>9043309</v>
+        <v>9043393</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.88877921898209511</v>
+        <v>0.88878747452820051</v>
       </c>
     </row>
     <row r="49" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -9817,16 +9817,24 @@
       <c r="BJ55"/>
     </row>
     <row r="56" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
@@ -9838,14 +9846,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2018-2019.xlsx
+++ b/gstdatabase/GSTR-3B-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2257CD6-ED67-467C-B02B-67AA584CF48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70DE3E9-14C5-48E8-B225-F82F3148E4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -388,14 +388,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -405,15 +414,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -754,12 +754,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -776,11 +776,11 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -806,14 +806,14 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
     </row>
     <row r="8" spans="1:62" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -905,7 +905,7 @@
       <c r="BJ8" s="19"/>
     </row>
     <row r="9" spans="1:62" s="11" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="19"/>
       <c r="C9" s="12" t="s">
         <v>3</v>
@@ -1256,14 +1256,14 @@
       </c>
       <c r="AX10" s="10">
         <f>AY10-AW10</f>
-        <v>38523</v>
+        <v>38524</v>
       </c>
       <c r="AY10" s="7">
-        <v>76795</v>
+        <v>76796</v>
       </c>
       <c r="AZ10" s="9">
         <f>AY10/AV10</f>
-        <v>0.89029423357833481</v>
+        <v>0.89030582670592873</v>
       </c>
       <c r="BA10" s="6">
         <v>87367</v>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="BC10" s="10">
         <f>BD10-BB10</f>
-        <v>19108</v>
+        <v>19109</v>
       </c>
       <c r="BD10" s="7">
-        <v>77565</v>
+        <v>77566</v>
       </c>
       <c r="BE10" s="9">
         <f>BD10/BA10</f>
-        <v>0.88780660890267493</v>
+        <v>0.88781805487197685</v>
       </c>
       <c r="BF10" s="6">
         <v>88878</v>
@@ -1290,14 +1290,14 @@
       </c>
       <c r="BH10" s="10">
         <f>BI10-BG10</f>
-        <v>36326</v>
+        <v>36327</v>
       </c>
       <c r="BI10" s="7">
-        <v>78505</v>
+        <v>78506</v>
       </c>
       <c r="BJ10" s="9">
         <f>BI10/BF10</f>
-        <v>0.88328945295798733</v>
+        <v>0.88330070433628116</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="AI15" s="10">
         <f t="shared" si="12"/>
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="AJ15" s="7">
-        <v>362280</v>
+        <v>362281</v>
       </c>
       <c r="AK15" s="9">
         <f t="shared" si="13"/>
-        <v>0.89261647403187772</v>
+        <v>0.8926189379174746</v>
       </c>
       <c r="AL15" s="4">
         <v>411169</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>127502</v>
+        <v>127503</v>
       </c>
       <c r="AT17" s="7">
-        <v>478899</v>
+        <v>478900</v>
       </c>
       <c r="AU17" s="9">
         <f t="shared" si="17"/>
-        <v>0.90257145764935143</v>
+        <v>0.90257334232954012</v>
       </c>
       <c r="AV17" s="6">
         <v>538347</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>162548</v>
+        <v>162549</v>
       </c>
       <c r="AY17" s="7">
-        <v>483871</v>
+        <v>483872</v>
       </c>
       <c r="AZ17" s="9">
         <f t="shared" si="19"/>
-        <v>0.89880876089213835</v>
+        <v>0.89881061843012033</v>
       </c>
       <c r="BA17" s="6">
         <v>545177</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>100823</v>
+        <v>100824</v>
       </c>
       <c r="BD17" s="7">
-        <v>489108</v>
+        <v>489109</v>
       </c>
       <c r="BE17" s="9">
         <f t="shared" si="21"/>
-        <v>0.89715450211582659</v>
+        <v>0.89715633638249592</v>
       </c>
       <c r="BF17" s="6">
         <v>551432</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>209688</v>
+        <v>209689</v>
       </c>
       <c r="BI17" s="7">
-        <v>493403</v>
+        <v>493404</v>
       </c>
       <c r="BJ17" s="9">
         <f t="shared" si="23"/>
-        <v>0.89476671647637429</v>
+        <v>0.89476852993660139</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>416758</v>
+        <v>416759</v>
       </c>
       <c r="F18" s="7">
-        <v>867167</v>
+        <v>867168</v>
       </c>
       <c r="G18" s="9">
         <f t="shared" si="1"/>
-        <v>0.91998714175682639</v>
+        <v>0.91998820266797932</v>
       </c>
       <c r="H18" s="4">
         <v>980551</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>214880</v>
+        <v>214881</v>
       </c>
       <c r="K18" s="7">
-        <v>889303</v>
+        <v>889304</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="3"/>
-        <v>0.90694211723816509</v>
+        <v>0.90694313707293139</v>
       </c>
       <c r="M18" s="4">
         <v>1006440</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>222985</v>
+        <v>222986</v>
       </c>
       <c r="P18" s="7">
-        <v>903685</v>
+        <v>903686</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="5"/>
-        <v>0.89790250784944958</v>
+        <v>0.89790350145065778</v>
       </c>
       <c r="R18" s="4">
         <v>1025384</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>174919</v>
+        <v>174920</v>
       </c>
       <c r="U18" s="7">
-        <v>917017</v>
+        <v>917018</v>
       </c>
       <c r="V18" s="9">
         <f t="shared" si="7"/>
-        <v>0.89431569051204229</v>
+        <v>0.89431666575643853</v>
       </c>
       <c r="W18" s="4">
         <v>1044299</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>254595</v>
+        <v>254596</v>
       </c>
       <c r="Z18" s="7">
-        <v>930886</v>
+        <v>930887</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="9"/>
-        <v>0.89139796169487862</v>
+        <v>0.89139891927503523</v>
       </c>
       <c r="AB18" s="4">
         <v>1050898</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>187476</v>
+        <v>187477</v>
       </c>
       <c r="AE18" s="7">
-        <v>943113</v>
+        <v>943114</v>
       </c>
       <c r="AF18" s="9">
         <f t="shared" si="11"/>
-        <v>0.89743533625527883</v>
+        <v>0.89743628782241469</v>
       </c>
       <c r="AG18" s="4">
         <v>1062525</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>256112</v>
+        <v>256113</v>
       </c>
       <c r="AJ18" s="7">
-        <v>957861</v>
+        <v>957862</v>
       </c>
       <c r="AK18" s="9">
         <f t="shared" si="13"/>
-        <v>0.90149502364650247</v>
+        <v>0.90149596480082816</v>
       </c>
       <c r="AL18" s="4">
         <v>1073550</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>218725</v>
+        <v>218726</v>
       </c>
       <c r="AO18" s="7">
-        <v>956528</v>
+        <v>956529</v>
       </c>
       <c r="AP18" s="9">
         <f t="shared" si="15"/>
-        <v>0.89099529598062499</v>
+        <v>0.89099622746961016</v>
       </c>
       <c r="AQ18" s="4">
         <v>1080975</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>233200</v>
+        <v>233201</v>
       </c>
       <c r="AT18" s="7">
-        <v>967314</v>
+        <v>967315</v>
       </c>
       <c r="AU18" s="9">
         <f t="shared" si="17"/>
-        <v>0.89485325747588984</v>
+        <v>0.89485418256666438</v>
       </c>
       <c r="AV18" s="6">
         <v>1090269</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="18"/>
-        <v>321388</v>
+        <v>321389</v>
       </c>
       <c r="AY18" s="7">
-        <v>975595</v>
+        <v>975596</v>
       </c>
       <c r="AZ18" s="9">
         <f t="shared" si="19"/>
-        <v>0.89482045256721043</v>
+        <v>0.89482136977204707</v>
       </c>
       <c r="BA18" s="6">
         <v>1099973</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>196057</v>
+        <v>196059</v>
       </c>
       <c r="BD18" s="7">
-        <v>982910</v>
+        <v>982912</v>
       </c>
       <c r="BE18" s="9">
         <f t="shared" si="21"/>
-        <v>0.89357647869538614</v>
+        <v>0.89357829692183355</v>
       </c>
       <c r="BF18" s="6">
         <v>1108438</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>378208</v>
+        <v>378210</v>
       </c>
       <c r="BI18" s="7">
-        <v>990074</v>
+        <v>990076</v>
       </c>
       <c r="BJ18" s="9">
         <f t="shared" si="23"/>
-        <v>0.89321549784471477</v>
+        <v>0.89321730218559814</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" si="0"/>
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="F21" s="7">
-        <v>7065</v>
+        <v>7066</v>
       </c>
       <c r="G21" s="9">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.83345128568058502</v>
       </c>
       <c r="H21" s="4">
         <v>8658</v>
@@ -3554,14 +3554,14 @@
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="14"/>
-        <v>4511</v>
+        <v>4512</v>
       </c>
       <c r="AO21" s="7">
-        <v>7885</v>
+        <v>7886</v>
       </c>
       <c r="AP21" s="9">
         <f t="shared" si="15"/>
-        <v>0.79325955734406439</v>
+        <v>0.79336016096579476</v>
       </c>
       <c r="AQ21" s="4">
         <v>10144</v>
@@ -3571,14 +3571,14 @@
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="16"/>
-        <v>4711</v>
+        <v>4712</v>
       </c>
       <c r="AT21" s="7">
-        <v>7996</v>
+        <v>7997</v>
       </c>
       <c r="AU21" s="9">
         <f t="shared" si="17"/>
-        <v>0.78824921135646686</v>
+        <v>0.78834779179810721</v>
       </c>
       <c r="AV21" s="6">
         <v>10345</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="BH26" s="10">
         <f t="shared" si="22"/>
-        <v>8224</v>
+        <v>8225</v>
       </c>
       <c r="BI26" s="7">
-        <v>19229</v>
+        <v>19230</v>
       </c>
       <c r="BJ26" s="9">
         <f t="shared" si="23"/>
-        <v>0.81124752141079193</v>
+        <v>0.81128971016327045</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="AS28" s="10">
         <f t="shared" si="16"/>
-        <v>137223</v>
+        <v>137224</v>
       </c>
       <c r="AT28" s="7">
-        <v>501842</v>
+        <v>501843</v>
       </c>
       <c r="AU28" s="9">
         <f t="shared" si="17"/>
-        <v>0.89833129862272165</v>
+        <v>0.89833308869070849</v>
       </c>
       <c r="AV28" s="6">
         <v>568213</v>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="18"/>
-        <v>164924</v>
+        <v>164925</v>
       </c>
       <c r="AY28" s="7">
-        <v>508404</v>
+        <v>508405</v>
       </c>
       <c r="AZ28" s="9">
         <f t="shared" si="19"/>
-        <v>0.89474193656252143</v>
+        <v>0.89474369646593799</v>
       </c>
       <c r="BA28" s="6">
         <v>575661</v>
@@ -5089,14 +5089,14 @@
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="20"/>
-        <v>113640</v>
+        <v>113641</v>
       </c>
       <c r="BD28" s="7">
-        <v>513684</v>
+        <v>513685</v>
       </c>
       <c r="BE28" s="9">
         <f t="shared" si="21"/>
-        <v>0.89233767790418317</v>
+        <v>0.89233941503766978</v>
       </c>
       <c r="BF28" s="6">
         <v>582519</v>
@@ -5106,14 +5106,14 @@
       </c>
       <c r="BH28" s="10">
         <f t="shared" si="22"/>
-        <v>208900</v>
+        <v>208901</v>
       </c>
       <c r="BI28" s="7">
-        <v>518272</v>
+        <v>518273</v>
       </c>
       <c r="BJ28" s="9">
         <f t="shared" si="23"/>
-        <v>0.88970831852694932</v>
+        <v>0.88971003520915193</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5462,14 +5462,14 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="14"/>
-        <v>58878</v>
+        <v>58879</v>
       </c>
       <c r="AO30" s="7">
-        <v>185948</v>
+        <v>185949</v>
       </c>
       <c r="AP30" s="9">
         <f t="shared" si="15"/>
-        <v>0.83747534161434734</v>
+        <v>0.83747984542907838</v>
       </c>
       <c r="AQ30" s="4">
         <v>223141</v>
@@ -5886,14 +5886,14 @@
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="14"/>
-        <v>93778</v>
+        <v>93779</v>
       </c>
       <c r="AO32" s="7">
-        <v>311836</v>
+        <v>311837</v>
       </c>
       <c r="AP32" s="9">
         <f t="shared" si="15"/>
-        <v>0.93250998041297228</v>
+        <v>0.93251297079888162</v>
       </c>
       <c r="AQ32" s="4">
         <v>335747</v>
@@ -5903,14 +5903,14 @@
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="16"/>
-        <v>98666</v>
+        <v>98667</v>
       </c>
       <c r="AT32" s="7">
-        <v>314705</v>
+        <v>314706</v>
       </c>
       <c r="AU32" s="9">
         <f t="shared" si="17"/>
-        <v>0.9373278093326225</v>
+        <v>0.93733078776578793</v>
       </c>
       <c r="AV32" s="6">
         <v>338656</v>
@@ -5979,14 +5979,14 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="0"/>
-        <v>401552</v>
+        <v>401553</v>
       </c>
       <c r="F33" s="7">
-        <v>722980</v>
+        <v>722981</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="1"/>
-        <v>0.94659758800786109</v>
+        <v>0.94659889730768676</v>
       </c>
       <c r="H33" s="4">
         <v>790674</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>204480</v>
+        <v>204481</v>
       </c>
       <c r="Z33" s="7">
-        <v>761131</v>
+        <v>761132</v>
       </c>
       <c r="AA33" s="9">
         <f t="shared" si="9"/>
-        <v>0.92926926345194028</v>
+        <v>0.92927048435775472</v>
       </c>
       <c r="AB33" s="4">
         <v>823883</v>
@@ -6081,14 +6081,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>226201</v>
+        <v>226202</v>
       </c>
       <c r="AJ33" s="7">
-        <v>773751</v>
+        <v>773752</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="13"/>
-        <v>0.93483526985442567</v>
+        <v>0.93483647804061198</v>
       </c>
       <c r="AL33" s="4">
         <v>833066</v>
@@ -6098,14 +6098,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>170645</v>
+        <v>170647</v>
       </c>
       <c r="AO33" s="7">
-        <v>774384</v>
+        <v>774386</v>
       </c>
       <c r="AP33" s="9">
         <f t="shared" si="15"/>
-        <v>0.92955900252801094</v>
+        <v>0.92956140329817805</v>
       </c>
       <c r="AQ33" s="4">
         <v>838229</v>
@@ -6132,14 +6132,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>217579</v>
+        <v>217580</v>
       </c>
       <c r="AY33" s="7">
-        <v>788687</v>
+        <v>788688</v>
       </c>
       <c r="AZ33" s="9">
         <f t="shared" si="19"/>
-        <v>0.9312634313378203</v>
+        <v>0.93126461211477152</v>
       </c>
       <c r="BA33" s="6">
         <v>854421</v>
@@ -6149,14 +6149,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>134194</v>
+        <v>134195</v>
       </c>
       <c r="BD33" s="7">
-        <v>795541</v>
+        <v>795542</v>
       </c>
       <c r="BE33" s="9">
         <f t="shared" si="21"/>
-        <v>0.93108783609017098</v>
+        <v>0.93108900647338955</v>
       </c>
       <c r="BF33" s="6">
         <v>864165</v>
@@ -6166,14 +6166,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>281123</v>
+        <v>281125</v>
       </c>
       <c r="BI33" s="7">
-        <v>802664</v>
+        <v>802666</v>
       </c>
       <c r="BJ33" s="9">
         <f t="shared" si="23"/>
-        <v>0.92883187817141399</v>
+        <v>0.92883419254424793</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6615,14 +6615,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>635201</v>
+        <v>635204</v>
       </c>
       <c r="F36" s="7">
-        <v>1117302</v>
+        <v>1117305</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="1"/>
-        <v>0.90621395792475512</v>
+        <v>0.90621639114502484</v>
       </c>
       <c r="H36" s="4">
         <v>1268548</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>364149</v>
+        <v>364150</v>
       </c>
       <c r="K36" s="7">
-        <v>1135867</v>
+        <v>1135868</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="3"/>
-        <v>0.89540718995260726</v>
+        <v>0.89540797825545426</v>
       </c>
       <c r="M36" s="4">
         <v>1291465</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>366227</v>
+        <v>366230</v>
       </c>
       <c r="P36" s="7">
-        <v>1150169</v>
+        <v>1150172</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="5"/>
-        <v>0.89059246669480008</v>
+        <v>0.89059478963812411</v>
       </c>
       <c r="R36" s="4">
         <v>1304709</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>303565</v>
+        <v>303566</v>
       </c>
       <c r="U36" s="7">
-        <v>1161622</v>
+        <v>1161623</v>
       </c>
       <c r="V36" s="9">
         <f t="shared" si="7"/>
-        <v>0.89033033419712748</v>
+        <v>0.89033110065156296</v>
       </c>
       <c r="W36" s="4">
         <v>1322652</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>444960</v>
+        <v>444961</v>
       </c>
       <c r="Z36" s="7">
-        <v>1173313</v>
+        <v>1173314</v>
       </c>
       <c r="AA36" s="9">
         <f t="shared" si="9"/>
-        <v>0.88709123790687194</v>
+        <v>0.88709199396364269</v>
       </c>
       <c r="AB36" s="4">
         <v>1322160</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>336122</v>
+        <v>336123</v>
       </c>
       <c r="AE36" s="7">
-        <v>1183573</v>
+        <v>1183574</v>
       </c>
       <c r="AF36" s="9">
         <f t="shared" si="11"/>
-        <v>0.89518136987959096</v>
+        <v>0.89518212621770432</v>
       </c>
       <c r="AG36" s="4">
         <v>1336822</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>409285</v>
+        <v>409286</v>
       </c>
       <c r="AJ36" s="7">
-        <v>1192845</v>
+        <v>1192846</v>
       </c>
       <c r="AK36" s="9">
         <f t="shared" si="13"/>
-        <v>0.89229904953688677</v>
+        <v>0.89229979757963285</v>
       </c>
       <c r="AL36" s="4">
         <v>1349209</v>
@@ -6734,14 +6734,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>349942</v>
+        <v>349943</v>
       </c>
       <c r="AO36" s="7">
-        <v>1189350</v>
+        <v>1189351</v>
       </c>
       <c r="AP36" s="9">
         <f t="shared" si="15"/>
-        <v>0.8815165033734581</v>
+        <v>0.88151724454847247</v>
       </c>
       <c r="AQ36" s="4">
         <v>1349417</v>
@@ -6751,14 +6751,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>371130</v>
+        <v>371131</v>
       </c>
       <c r="AT36" s="7">
-        <v>1201604</v>
+        <v>1201605</v>
       </c>
       <c r="AU36" s="9">
         <f t="shared" si="17"/>
-        <v>0.89046158452131552</v>
+        <v>0.89046232558208471</v>
       </c>
       <c r="AV36" s="6">
         <v>1347780</v>
@@ -6768,14 +6768,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>460662</v>
+        <v>460663</v>
       </c>
       <c r="AY36" s="7">
-        <v>1211605</v>
+        <v>1211606</v>
       </c>
       <c r="AZ36" s="9">
         <f t="shared" si="19"/>
-        <v>0.89896348068675902</v>
+        <v>0.89896422264761311</v>
       </c>
       <c r="BA36" s="6">
         <v>1364152</v>
@@ -6785,14 +6785,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>293544</v>
+        <v>293545</v>
       </c>
       <c r="BD36" s="7">
-        <v>1221219</v>
+        <v>1221220</v>
       </c>
       <c r="BE36" s="9">
         <f t="shared" si="21"/>
-        <v>0.89522208668828696</v>
+        <v>0.8952228197444273</v>
       </c>
       <c r="BF36" s="6">
         <v>1384075</v>
@@ -6802,14 +6802,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="22"/>
-        <v>511477</v>
+        <v>511478</v>
       </c>
       <c r="BI36" s="7">
-        <v>1229539</v>
+        <v>1229540</v>
       </c>
       <c r="BJ36" s="9">
         <f t="shared" si="23"/>
-        <v>0.88834709101746656</v>
+        <v>0.88834781352166614</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6827,14 +6827,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>356712</v>
+        <v>356715</v>
       </c>
       <c r="F37" s="7">
-        <v>552279</v>
+        <v>552282</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="1"/>
-        <v>0.89440067370057574</v>
+        <v>0.89440553211818907</v>
       </c>
       <c r="H37" s="4">
         <v>636289</v>
@@ -6844,14 +6844,14 @@
       </c>
       <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v>165068</v>
+        <v>165071</v>
       </c>
       <c r="K37" s="7">
-        <v>560831</v>
+        <v>560834</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="3"/>
-        <v>0.88140923385442782</v>
+        <v>0.88141394869312528</v>
       </c>
       <c r="M37" s="4">
         <v>650458</v>
@@ -6861,14 +6861,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>166951</v>
+        <v>166954</v>
       </c>
       <c r="P37" s="7">
-        <v>569066</v>
+        <v>569069</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="5"/>
-        <v>0.87486970719093315</v>
+        <v>0.87487431932576742</v>
       </c>
       <c r="R37" s="4">
         <v>663657</v>
@@ -6878,14 +6878,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>133640</v>
+        <v>133643</v>
       </c>
       <c r="U37" s="7">
-        <v>578191</v>
+        <v>578194</v>
       </c>
       <c r="V37" s="9">
         <f t="shared" si="7"/>
-        <v>0.87121962097890926</v>
+        <v>0.87122414138628845</v>
       </c>
       <c r="W37" s="4">
         <v>677316</v>
@@ -6895,14 +6895,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>185289</v>
+        <v>185292</v>
       </c>
       <c r="Z37" s="7">
-        <v>587377</v>
+        <v>587380</v>
       </c>
       <c r="AA37" s="9">
         <f t="shared" si="9"/>
-        <v>0.86721264520548758</v>
+        <v>0.86721707445269269</v>
       </c>
       <c r="AB37" s="4">
         <v>682420</v>
@@ -6912,14 +6912,14 @@
       </c>
       <c r="AD37" s="10">
         <f t="shared" si="10"/>
-        <v>150857</v>
+        <v>150860</v>
       </c>
       <c r="AE37" s="7">
-        <v>594944</v>
+        <v>594947</v>
       </c>
       <c r="AF37" s="9">
         <f t="shared" si="11"/>
-        <v>0.87181501128337391</v>
+        <v>0.87181940740306552</v>
       </c>
       <c r="AG37" s="4">
         <v>691854</v>
@@ -6929,14 +6929,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>185426</v>
+        <v>185429</v>
       </c>
       <c r="AJ37" s="7">
-        <v>603109</v>
+        <v>603112</v>
       </c>
       <c r="AK37" s="9">
         <f t="shared" si="13"/>
-        <v>0.87172871733053503</v>
+        <v>0.87173305350550834</v>
       </c>
       <c r="AL37" s="4">
         <v>698331</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>163061</v>
+        <v>163065</v>
       </c>
       <c r="AO37" s="7">
-        <v>603940</v>
+        <v>603944</v>
       </c>
       <c r="AP37" s="9">
         <f t="shared" si="15"/>
-        <v>0.86483343858428163</v>
+        <v>0.86483916652704806</v>
       </c>
       <c r="AQ37" s="4">
         <v>700400</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>175159</v>
+        <v>175162</v>
       </c>
       <c r="AT37" s="7">
-        <v>611988</v>
+        <v>611991</v>
       </c>
       <c r="AU37" s="9">
         <f t="shared" si="17"/>
-        <v>0.87376927470017129</v>
+        <v>0.87377355796687606</v>
       </c>
       <c r="AV37" s="6">
         <v>698615</v>
@@ -6980,14 +6980,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>212636</v>
+        <v>212638</v>
       </c>
       <c r="AY37" s="7">
-        <v>619449</v>
+        <v>619451</v>
       </c>
       <c r="AZ37" s="9">
         <f t="shared" si="19"/>
-        <v>0.88668150555026737</v>
+        <v>0.88668436835739284</v>
       </c>
       <c r="BA37" s="6">
         <v>701194</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>123319</v>
+        <v>123323</v>
       </c>
       <c r="BD37" s="7">
-        <v>626355</v>
+        <v>626359</v>
       </c>
       <c r="BE37" s="9">
         <f t="shared" si="21"/>
-        <v>0.89326919511575964</v>
+        <v>0.89327489967113238</v>
       </c>
       <c r="BF37" s="6">
         <v>706472</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="22"/>
-        <v>257258</v>
+        <v>257262</v>
       </c>
       <c r="BI37" s="7">
-        <v>632157</v>
+        <v>632161</v>
       </c>
       <c r="BJ37" s="9">
         <f t="shared" si="23"/>
-        <v>0.89480828681108382</v>
+        <v>0.89481394874814568</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7463,14 +7463,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="0"/>
-        <v>154110</v>
+        <v>154111</v>
       </c>
       <c r="F40" s="7">
-        <v>239015</v>
+        <v>239016</v>
       </c>
       <c r="G40" s="9">
         <f t="shared" si="1"/>
-        <v>0.94789671350330951</v>
+        <v>0.94790067934944255</v>
       </c>
       <c r="H40" s="4">
         <v>258924</v>
@@ -7675,14 +7675,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>385851</v>
+        <v>385856</v>
       </c>
       <c r="F41" s="7">
-        <v>690937</v>
+        <v>690942</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="1"/>
-        <v>0.85039446639343252</v>
+        <v>0.85040062031532693</v>
       </c>
       <c r="H41" s="4">
         <v>835051</v>
@@ -7692,14 +7692,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>211143</v>
+        <v>211148</v>
       </c>
       <c r="K41" s="7">
-        <v>701663</v>
+        <v>701668</v>
       </c>
       <c r="L41" s="9">
         <f t="shared" si="3"/>
-        <v>0.84026364856757252</v>
+        <v>0.84026963622581141</v>
       </c>
       <c r="M41" s="4">
         <v>852643</v>
@@ -7709,14 +7709,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>211053</v>
+        <v>211057</v>
       </c>
       <c r="P41" s="7">
-        <v>709923</v>
+        <v>709927</v>
       </c>
       <c r="Q41" s="9">
         <f t="shared" si="5"/>
-        <v>0.83261458781694098</v>
+        <v>0.83261927911212552</v>
       </c>
       <c r="R41" s="4">
         <v>868359</v>
@@ -7726,14 +7726,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171927</v>
+        <v>171930</v>
       </c>
       <c r="U41" s="7">
-        <v>719474</v>
+        <v>719477</v>
       </c>
       <c r="V41" s="9">
         <f t="shared" si="7"/>
-        <v>0.82854441538580237</v>
+        <v>0.8285478701781176</v>
       </c>
       <c r="W41" s="4">
         <v>879806</v>
@@ -7743,14 +7743,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>230058</v>
+        <v>230061</v>
       </c>
       <c r="Z41" s="7">
-        <v>727717</v>
+        <v>727720</v>
       </c>
       <c r="AA41" s="9">
         <f t="shared" si="9"/>
-        <v>0.82713348169937462</v>
+        <v>0.82713689154199899</v>
       </c>
       <c r="AB41" s="4">
         <v>882248</v>
@@ -7760,14 +7760,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>187410</v>
+        <v>187414</v>
       </c>
       <c r="AE41" s="7">
-        <v>735473</v>
+        <v>735477</v>
       </c>
       <c r="AF41" s="9">
         <f t="shared" si="11"/>
-        <v>0.8336352136814138</v>
+        <v>0.83363974755397574</v>
       </c>
       <c r="AG41" s="4">
         <v>877145</v>
@@ -7777,14 +7777,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>242416</v>
+        <v>242423</v>
       </c>
       <c r="AJ41" s="7">
-        <v>743278</v>
+        <v>743285</v>
       </c>
       <c r="AK41" s="9">
         <f t="shared" si="13"/>
-        <v>0.84738327186497098</v>
+        <v>0.84739125230150092</v>
       </c>
       <c r="AL41" s="4">
         <v>875890</v>
@@ -7794,14 +7794,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>205241</v>
+        <v>205249</v>
       </c>
       <c r="AO41" s="7">
-        <v>742086</v>
+        <v>742094</v>
       </c>
       <c r="AP41" s="9">
         <f t="shared" si="15"/>
-        <v>0.8472365251344347</v>
+        <v>0.84724565870143509</v>
       </c>
       <c r="AQ41" s="4">
         <v>865402</v>
@@ -7811,14 +7811,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>247883</v>
+        <v>247890</v>
       </c>
       <c r="AT41" s="7">
-        <v>748351</v>
+        <v>748358</v>
       </c>
       <c r="AU41" s="9">
         <f t="shared" si="17"/>
-        <v>0.86474378381376515</v>
+        <v>0.8647518725401605</v>
       </c>
       <c r="AV41" s="6">
         <v>863602</v>
@@ -7828,14 +7828,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>252922</v>
+        <v>252926</v>
       </c>
       <c r="AY41" s="7">
-        <v>753200</v>
+        <v>753204</v>
       </c>
       <c r="AZ41" s="9">
         <f t="shared" si="19"/>
-        <v>0.87216101861737239</v>
+        <v>0.87216565038061511</v>
       </c>
       <c r="BA41" s="6">
         <v>853803</v>
@@ -7845,14 +7845,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>156258</v>
+        <v>156262</v>
       </c>
       <c r="BD41" s="7">
-        <v>759995</v>
+        <v>759999</v>
       </c>
       <c r="BE41" s="9">
         <f t="shared" si="21"/>
-        <v>0.89012922184625731</v>
+        <v>0.89013390676772042</v>
       </c>
       <c r="BF41" s="6">
         <v>867754</v>
@@ -7862,14 +7862,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="22"/>
-        <v>339120</v>
+        <v>339125</v>
       </c>
       <c r="BI41" s="7">
-        <v>767266</v>
+        <v>767271</v>
       </c>
       <c r="BJ41" s="9">
         <f t="shared" si="23"/>
-        <v>0.88419759517098162</v>
+        <v>0.88420335717265497</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="E42" s="10">
         <f t="shared" si="0"/>
-        <v>9635</v>
+        <v>9637</v>
       </c>
       <c r="F42" s="7">
-        <v>16364</v>
+        <v>16366</v>
       </c>
       <c r="G42" s="9">
         <f t="shared" si="1"/>
-        <v>0.87056445177421926</v>
+        <v>0.87067085173165926</v>
       </c>
       <c r="H42" s="4">
         <v>19351</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="J42" s="10">
         <f t="shared" si="2"/>
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="K42" s="7">
-        <v>16618</v>
+        <v>16620</v>
       </c>
       <c r="L42" s="9">
         <f t="shared" si="3"/>
-        <v>0.85876698878610924</v>
+        <v>0.85887034261795259</v>
       </c>
       <c r="M42" s="4">
         <v>19723</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="O42" s="10">
         <f t="shared" si="4"/>
-        <v>5457</v>
+        <v>5459</v>
       </c>
       <c r="P42" s="7">
-        <v>16751</v>
+        <v>16753</v>
       </c>
       <c r="Q42" s="9">
         <f t="shared" si="5"/>
-        <v>0.84931298484003448</v>
+        <v>0.84941438929168989</v>
       </c>
       <c r="R42" s="4">
         <v>19929</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="T42" s="10">
         <f t="shared" si="6"/>
-        <v>4549</v>
+        <v>4551</v>
       </c>
       <c r="U42" s="7">
-        <v>16950</v>
+        <v>16952</v>
       </c>
       <c r="V42" s="9">
         <f t="shared" si="7"/>
-        <v>0.85051934367002857</v>
+        <v>0.85061969993476838</v>
       </c>
       <c r="W42" s="4">
         <v>20172</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="Y42" s="10">
         <f t="shared" si="8"/>
-        <v>6191</v>
+        <v>6193</v>
       </c>
       <c r="Z42" s="7">
-        <v>17073</v>
+        <v>17075</v>
       </c>
       <c r="AA42" s="9">
         <f t="shared" si="9"/>
-        <v>0.84637120761451512</v>
+        <v>0.84647035494745193</v>
       </c>
       <c r="AB42" s="4">
         <v>20242</v>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="AD42" s="10">
         <f t="shared" si="10"/>
-        <v>4524</v>
+        <v>4526</v>
       </c>
       <c r="AE42" s="7">
-        <v>17187</v>
+        <v>17189</v>
       </c>
       <c r="AF42" s="9">
         <f t="shared" si="11"/>
-        <v>0.84907617824325654</v>
+        <v>0.84917498270921843</v>
       </c>
       <c r="AG42" s="4">
         <v>20402</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="AI42" s="10">
         <f t="shared" si="12"/>
-        <v>6142</v>
+        <v>6144</v>
       </c>
       <c r="AJ42" s="7">
-        <v>17360</v>
+        <v>17362</v>
       </c>
       <c r="AK42" s="9">
         <f t="shared" si="13"/>
-        <v>0.85089697088520733</v>
+        <v>0.85099500049014798</v>
       </c>
       <c r="AL42" s="4">
         <v>20463</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="AN42" s="10">
         <f t="shared" si="14"/>
-        <v>5439</v>
+        <v>5441</v>
       </c>
       <c r="AO42" s="7">
-        <v>17252</v>
+        <v>17254</v>
       </c>
       <c r="AP42" s="9">
         <f t="shared" si="15"/>
-        <v>0.84308263695450325</v>
+        <v>0.84318037433416415</v>
       </c>
       <c r="AQ42" s="4">
         <v>20448</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="AS42" s="10">
         <f t="shared" si="16"/>
-        <v>6336</v>
+        <v>6338</v>
       </c>
       <c r="AT42" s="7">
-        <v>17315</v>
+        <v>17317</v>
       </c>
       <c r="AU42" s="9">
         <f t="shared" si="17"/>
-        <v>0.84678208137715183</v>
+        <v>0.84687989045383416</v>
       </c>
       <c r="AV42" s="6">
         <v>20536</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="AX42" s="10">
         <f t="shared" si="18"/>
-        <v>7169</v>
+        <v>7171</v>
       </c>
       <c r="AY42" s="7">
-        <v>17305</v>
+        <v>17307</v>
       </c>
       <c r="AZ42" s="9">
         <f t="shared" si="19"/>
-        <v>0.84266653681340087</v>
+        <v>0.84276392676275813</v>
       </c>
       <c r="BA42" s="6">
         <v>20618</v>
@@ -8057,14 +8057,14 @@
       </c>
       <c r="BC42" s="10">
         <f t="shared" si="20"/>
-        <v>4110</v>
+        <v>4112</v>
       </c>
       <c r="BD42" s="7">
-        <v>17414</v>
+        <v>17416</v>
       </c>
       <c r="BE42" s="9">
         <f t="shared" si="21"/>
-        <v>0.84460180424871467</v>
+        <v>0.84469880686778542</v>
       </c>
       <c r="BF42" s="6">
         <v>20839</v>
@@ -8074,14 +8074,14 @@
       </c>
       <c r="BH42" s="10">
         <f t="shared" si="22"/>
-        <v>8073</v>
+        <v>8075</v>
       </c>
       <c r="BI42" s="7">
-        <v>17535</v>
+        <v>17537</v>
       </c>
       <c r="BJ42" s="9">
         <f t="shared" si="23"/>
-        <v>0.84145112529392008</v>
+        <v>0.8415470991890206</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8430,14 +8430,14 @@
       </c>
       <c r="AN44" s="10">
         <f t="shared" si="14"/>
-        <v>90730</v>
+        <v>90731</v>
       </c>
       <c r="AO44" s="7">
-        <v>264395</v>
+        <v>264396</v>
       </c>
       <c r="AP44" s="9">
         <f t="shared" si="15"/>
-        <v>0.86676654558806177</v>
+        <v>0.8667698238896393</v>
       </c>
       <c r="AQ44" s="4">
         <v>305678</v>
@@ -8447,14 +8447,14 @@
       </c>
       <c r="AS44" s="10">
         <f t="shared" si="16"/>
-        <v>97407</v>
+        <v>97408</v>
       </c>
       <c r="AT44" s="7">
-        <v>267058</v>
+        <v>267059</v>
       </c>
       <c r="AU44" s="9">
         <f t="shared" si="17"/>
-        <v>0.87365790145185451</v>
+        <v>0.87366117286818157</v>
       </c>
       <c r="AV44" s="6">
         <v>308055</v>
@@ -9121,10 +9121,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="21"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="13">
         <f>SUM(C10:C47)</f>
         <v>8817798</v>
@@ -9135,15 +9135,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>4591851</v>
+        <v>4591868</v>
       </c>
       <c r="F48" s="13">
         <f>SUM(F10:F47)</f>
-        <v>8024169</v>
+        <v>8024186</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.90999691759779477</v>
+        <v>0.90999884551676058</v>
       </c>
       <c r="H48" s="13">
         <f>SUM(H10:H47)</f>
@@ -9155,15 +9155,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>2452776</v>
+        <v>2452788</v>
       </c>
       <c r="K48" s="13">
         <f>SUM(K10:K47)</f>
-        <v>8179216</v>
+        <v>8179228</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.89661685435123939</v>
+        <v>0.89661816980766607</v>
       </c>
       <c r="M48" s="13">
         <f>SUM(M10:M47)</f>
@@ -9175,15 +9175,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2507189</v>
+        <v>2507202</v>
       </c>
       <c r="P48" s="13">
         <f>SUM(P10:P47)</f>
-        <v>8297512</v>
+        <v>8297525</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.89060537464405354</v>
+        <v>0.89060676998640076</v>
       </c>
       <c r="R48" s="13">
         <f>SUM(R10:R47)</f>
@@ -9195,15 +9195,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>2026658</v>
+        <v>2026668</v>
       </c>
       <c r="U48" s="13">
         <f>SUM(U10:U47)</f>
-        <v>8410308</v>
+        <v>8410318</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.88807366031972435</v>
+        <v>0.88807471625448953</v>
       </c>
       <c r="W48" s="13">
         <f>SUM(W10:W47)</f>
@@ -9215,15 +9215,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>2872121</v>
+        <v>2872132</v>
       </c>
       <c r="Z48" s="13">
         <f>SUM(Z10:Z47)</f>
-        <v>8522361</v>
+        <v>8522372</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.88633583258634463</v>
+        <v>0.8863369765996244</v>
       </c>
       <c r="AB48" s="13">
         <f>SUM(AB10:AB47)</f>
@@ -9235,15 +9235,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2247995</v>
+        <v>2248006</v>
       </c>
       <c r="AE48" s="13">
         <f>SUM(AE10:AE47)</f>
-        <v>8617249</v>
+        <v>8617260</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.89230979993350068</v>
+        <v>0.89231093897541525</v>
       </c>
       <c r="AG48" s="13">
         <f>SUM(AG10:AG47)</f>
@@ -9255,15 +9255,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2832573</v>
+        <v>2832589</v>
       </c>
       <c r="AJ48" s="13">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8715238</v>
+        <v>8715254</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.89316848786758796</v>
+        <v>0.8931701276043118</v>
       </c>
       <c r="AL48" s="13">
         <f>SUM(AL10:AL47)</f>
@@ -9275,15 +9275,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2422672</v>
+        <v>2422694</v>
       </c>
       <c r="AO48" s="13">
         <f>SUM(AO10:AO47)</f>
-        <v>8713033</v>
+        <v>8713055</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.88487327409488203</v>
+        <v>0.88487550835843076</v>
       </c>
       <c r="AQ48" s="13">
         <f>SUM(AQ10:AQ47)</f>
@@ -9295,15 +9295,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>2607052</v>
+        <v>2607071</v>
       </c>
       <c r="AT48" s="13">
         <f>SUM(AT10:AT47)</f>
-        <v>8806508</v>
+        <v>8806527</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.88936686205822924</v>
+        <v>0.88936878086309257</v>
       </c>
       <c r="AV48" s="13">
         <f>SUM(AV10:AV47)</f>
@@ -9315,15 +9315,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>3160738</v>
+        <v>3160752</v>
       </c>
       <c r="AY48" s="13">
         <f>SUM(AY10:AY47)</f>
-        <v>8886739</v>
+        <v>8886753</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.89111207173948637</v>
+        <v>0.89111347558053589</v>
       </c>
       <c r="BA48" s="13">
         <f>SUM(BA10:BA47)</f>
@@ -9335,15 +9335,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2003733</v>
+        <v>2003750</v>
       </c>
       <c r="BD48" s="13">
         <f>SUM(BD10:BD47)</f>
-        <v>8966987</v>
+        <v>8967004</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.89185743031104259</v>
+        <v>0.89185912113275512</v>
       </c>
       <c r="BF48" s="13">
         <f>SUM(BF10:BF47)</f>
@@ -9355,15 +9355,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>3828566</v>
+        <v>3828586</v>
       </c>
       <c r="BI48" s="13">
         <f>SUM(BI10:BI47)</f>
-        <v>9043393</v>
+        <v>9043413</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.88878747452820051</v>
+        <v>0.88878944013441596</v>
       </c>
     </row>
     <row r="49" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -9817,24 +9817,16 @@
       <c r="BJ55"/>
     </row>
     <row r="56" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
@@ -9846,6 +9838,14 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2018-2019.xlsx
+++ b/gstdatabase/GSTR-3B-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70DE3E9-14C5-48E8-B225-F82F3148E4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B90B1E5-C6D1-4A70-86E8-27267A5D1F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -388,23 +388,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -414,6 +405,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -700,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK56"/>
+  <dimension ref="A1:BJ54"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -754,12 +754,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -776,11 +776,11 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -806,14 +806,14 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
     </row>
     <row r="8" spans="1:62" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -905,7 +905,7 @@
       <c r="BJ8" s="19"/>
     </row>
     <row r="9" spans="1:62" s="11" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="19"/>
       <c r="C9" s="12" t="s">
         <v>3</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>162549</v>
+        <v>162551</v>
       </c>
       <c r="AY17" s="7">
-        <v>483872</v>
+        <v>483874</v>
       </c>
       <c r="AZ17" s="9">
         <f t="shared" si="19"/>
-        <v>0.89881061843012033</v>
+        <v>0.89881433350608442</v>
       </c>
       <c r="BA17" s="6">
         <v>545177</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>100824</v>
+        <v>100825</v>
       </c>
       <c r="BD17" s="7">
-        <v>489109</v>
+        <v>489110</v>
       </c>
       <c r="BE17" s="9">
         <f t="shared" si="21"/>
-        <v>0.89715633638249592</v>
+        <v>0.89715817064916537</v>
       </c>
       <c r="BF17" s="6">
         <v>551432</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>209689</v>
+        <v>209690</v>
       </c>
       <c r="BI17" s="7">
-        <v>493404</v>
+        <v>493405</v>
       </c>
       <c r="BJ17" s="9">
         <f t="shared" si="23"/>
-        <v>0.89476852993660139</v>
+        <v>0.89477034339682859</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>218726</v>
+        <v>218727</v>
       </c>
       <c r="AO18" s="7">
-        <v>956529</v>
+        <v>956530</v>
       </c>
       <c r="AP18" s="9">
         <f t="shared" si="15"/>
-        <v>0.89099622746961016</v>
+        <v>0.89099715895859533</v>
       </c>
       <c r="AQ18" s="4">
         <v>1080975</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>233201</v>
+        <v>233202</v>
       </c>
       <c r="AT18" s="7">
-        <v>967315</v>
+        <v>967316</v>
       </c>
       <c r="AU18" s="9">
         <f t="shared" si="17"/>
-        <v>0.89485418256666438</v>
+        <v>0.89485510765743892</v>
       </c>
       <c r="AV18" s="6">
         <v>1090269</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>378210</v>
+        <v>378211</v>
       </c>
       <c r="BI18" s="7">
-        <v>990076</v>
+        <v>990077</v>
       </c>
       <c r="BJ18" s="9">
         <f t="shared" si="23"/>
-        <v>0.89321730218559814</v>
+        <v>0.89321820435603971</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" si="0"/>
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="F21" s="7">
-        <v>7066</v>
+        <v>7067</v>
       </c>
       <c r="G21" s="9">
         <f t="shared" si="1"/>
-        <v>0.83345128568058502</v>
+        <v>0.83356923802783678</v>
       </c>
       <c r="H21" s="4">
         <v>8658</v>
@@ -3452,14 +3452,14 @@
       </c>
       <c r="J21" s="10">
         <f t="shared" si="2"/>
-        <v>4657</v>
+        <v>4658</v>
       </c>
       <c r="K21" s="7">
-        <v>7248</v>
+        <v>7249</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="3"/>
-        <v>0.83714483714483712</v>
+        <v>0.83726033726033722</v>
       </c>
       <c r="M21" s="4">
         <v>9000</v>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="O21" s="10">
         <f t="shared" si="4"/>
-        <v>4689</v>
+        <v>4690</v>
       </c>
       <c r="P21" s="7">
-        <v>7387</v>
+        <v>7388</v>
       </c>
       <c r="Q21" s="9">
         <f t="shared" si="5"/>
-        <v>0.82077777777777783</v>
+        <v>0.82088888888888889</v>
       </c>
       <c r="R21" s="4">
         <v>9200</v>
@@ -3486,14 +3486,14 @@
       </c>
       <c r="T21" s="10">
         <f t="shared" si="6"/>
-        <v>4254</v>
+        <v>4255</v>
       </c>
       <c r="U21" s="7">
-        <v>7514</v>
+        <v>7515</v>
       </c>
       <c r="V21" s="9">
         <f t="shared" si="7"/>
-        <v>0.81673913043478263</v>
+        <v>0.8168478260869565</v>
       </c>
       <c r="W21" s="4">
         <v>9390</v>
@@ -3503,14 +3503,14 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="8"/>
-        <v>4732</v>
+        <v>4733</v>
       </c>
       <c r="Z21" s="7">
-        <v>7647</v>
+        <v>7648</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" si="9"/>
-        <v>0.81437699680511177</v>
+        <v>0.81448349307774226</v>
       </c>
       <c r="AB21" s="4">
         <v>9574</v>
@@ -3520,14 +3520,14 @@
       </c>
       <c r="AD21" s="10">
         <f t="shared" si="10"/>
-        <v>4389</v>
+        <v>4390</v>
       </c>
       <c r="AE21" s="7">
-        <v>7771</v>
+        <v>7772</v>
       </c>
       <c r="AF21" s="9">
         <f t="shared" si="11"/>
-        <v>0.81167745978692296</v>
+        <v>0.81178190933778982</v>
       </c>
       <c r="AG21" s="4">
         <v>9762</v>
@@ -3537,14 +3537,14 @@
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="12"/>
-        <v>4797</v>
+        <v>4798</v>
       </c>
       <c r="AJ21" s="7">
-        <v>7894</v>
+        <v>7895</v>
       </c>
       <c r="AK21" s="9">
         <f t="shared" si="13"/>
-        <v>0.80864576930956766</v>
+        <v>0.80874820733456254</v>
       </c>
       <c r="AL21" s="4">
         <v>9940</v>
@@ -3554,14 +3554,14 @@
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="14"/>
-        <v>4512</v>
+        <v>4513</v>
       </c>
       <c r="AO21" s="7">
-        <v>7886</v>
+        <v>7887</v>
       </c>
       <c r="AP21" s="9">
         <f t="shared" si="15"/>
-        <v>0.79336016096579476</v>
+        <v>0.79346076458752512</v>
       </c>
       <c r="AQ21" s="4">
         <v>10144</v>
@@ -3571,14 +3571,14 @@
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="16"/>
-        <v>4712</v>
+        <v>4713</v>
       </c>
       <c r="AT21" s="7">
-        <v>7997</v>
+        <v>7998</v>
       </c>
       <c r="AU21" s="9">
         <f t="shared" si="17"/>
-        <v>0.78834779179810721</v>
+        <v>0.78844637223974767</v>
       </c>
       <c r="AV21" s="6">
         <v>10345</v>
@@ -3588,14 +3588,14 @@
       </c>
       <c r="AX21" s="10">
         <f t="shared" si="18"/>
-        <v>4806</v>
+        <v>4807</v>
       </c>
       <c r="AY21" s="7">
-        <v>8089</v>
+        <v>8090</v>
       </c>
       <c r="AZ21" s="9">
         <f t="shared" si="19"/>
-        <v>0.78192363460608993</v>
+        <v>0.7820202996616723</v>
       </c>
       <c r="BA21" s="6">
         <v>10561</v>
@@ -3605,14 +3605,14 @@
       </c>
       <c r="BC21" s="10">
         <f t="shared" si="20"/>
-        <v>4205</v>
+        <v>4206</v>
       </c>
       <c r="BD21" s="7">
-        <v>8196</v>
+        <v>8197</v>
       </c>
       <c r="BE21" s="9">
         <f t="shared" si="21"/>
-        <v>0.77606287283401199</v>
+        <v>0.7761575608370419</v>
       </c>
       <c r="BF21" s="6">
         <v>10737</v>
@@ -3622,14 +3622,14 @@
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="22"/>
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="BI21" s="7">
-        <v>8352</v>
+        <v>8353</v>
       </c>
       <c r="BJ21" s="9">
         <f t="shared" si="23"/>
-        <v>0.7778709136630344</v>
+        <v>0.7779640495482909</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="AS23" s="10">
         <f t="shared" si="16"/>
-        <v>4050</v>
+        <v>4051</v>
       </c>
       <c r="AT23" s="7">
-        <v>7609</v>
+        <v>7610</v>
       </c>
       <c r="AU23" s="9">
         <f t="shared" si="17"/>
-        <v>0.73269138180067406</v>
+        <v>0.73278767453057292</v>
       </c>
       <c r="AV23" s="6">
         <v>10603</v>
@@ -4071,14 +4071,14 @@
       </c>
       <c r="E24" s="10">
         <f t="shared" si="0"/>
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="F24" s="7">
-        <v>3445</v>
+        <v>3447</v>
       </c>
       <c r="G24" s="9">
         <f t="shared" si="1"/>
-        <v>0.80565949485500465</v>
+        <v>0.80612722170252571</v>
       </c>
       <c r="H24" s="4">
         <v>4461</v>
@@ -4088,14 +4088,14 @@
       </c>
       <c r="J24" s="10">
         <f t="shared" si="2"/>
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="K24" s="7">
-        <v>3544</v>
+        <v>3545</v>
       </c>
       <c r="L24" s="9">
         <f t="shared" si="3"/>
-        <v>0.79444070836135394</v>
+        <v>0.79466487334678326</v>
       </c>
       <c r="M24" s="4">
         <v>4577</v>
@@ -4105,14 +4105,14 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="4"/>
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="P24" s="7">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="5"/>
-        <v>0.7878523050032773</v>
+        <v>0.78807078872623992</v>
       </c>
       <c r="R24" s="4">
         <v>4676</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="T24" s="10">
         <f t="shared" si="6"/>
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="U24" s="7">
-        <v>3666</v>
+        <v>3668</v>
       </c>
       <c r="V24" s="9">
         <f t="shared" si="7"/>
-        <v>0.78400342172797266</v>
+        <v>0.78443113772455086</v>
       </c>
       <c r="W24" s="4">
         <v>4739</v>
@@ -4139,14 +4139,14 @@
       </c>
       <c r="Y24" s="10">
         <f t="shared" si="8"/>
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="Z24" s="7">
-        <v>3716</v>
+        <v>3719</v>
       </c>
       <c r="AA24" s="9">
         <f t="shared" si="9"/>
-        <v>0.78413167334880773</v>
+        <v>0.78476471829499894</v>
       </c>
       <c r="AB24" s="4">
         <v>4810</v>
@@ -4156,14 +4156,14 @@
       </c>
       <c r="AD24" s="10">
         <f t="shared" si="10"/>
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="AE24" s="7">
-        <v>3774</v>
+        <v>3776</v>
       </c>
       <c r="AF24" s="9">
         <f t="shared" si="11"/>
-        <v>0.7846153846153846</v>
+        <v>0.78503118503118507</v>
       </c>
       <c r="AG24" s="4">
         <v>4912</v>
@@ -4173,14 +4173,14 @@
       </c>
       <c r="AI24" s="10">
         <f t="shared" si="12"/>
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="AJ24" s="7">
-        <v>3877</v>
+        <v>3879</v>
       </c>
       <c r="AK24" s="9">
         <f t="shared" si="13"/>
-        <v>0.78929153094462545</v>
+        <v>0.7896986970684039</v>
       </c>
       <c r="AL24" s="4">
         <v>5025</v>
@@ -4190,14 +4190,14 @@
       </c>
       <c r="AN24" s="10">
         <f t="shared" si="14"/>
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="AO24" s="7">
-        <v>3946</v>
+        <v>3948</v>
       </c>
       <c r="AP24" s="9">
         <f t="shared" si="15"/>
-        <v>0.78527363184079602</v>
+        <v>0.78567164179104476</v>
       </c>
       <c r="AQ24" s="4">
         <v>5062</v>
@@ -4207,14 +4207,14 @@
       </c>
       <c r="AS24" s="10">
         <f t="shared" si="16"/>
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="AT24" s="7">
-        <v>3990</v>
+        <v>3992</v>
       </c>
       <c r="AU24" s="9">
         <f t="shared" si="17"/>
-        <v>0.78822599762939549</v>
+        <v>0.78862109838008687</v>
       </c>
       <c r="AV24" s="6">
         <v>5081</v>
@@ -4224,14 +4224,14 @@
       </c>
       <c r="AX24" s="10">
         <f t="shared" si="18"/>
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="AY24" s="7">
-        <v>4034</v>
+        <v>4035</v>
       </c>
       <c r="AZ24" s="9">
         <f t="shared" si="19"/>
-        <v>0.79393820114150759</v>
+        <v>0.79413501279275733</v>
       </c>
       <c r="BA24" s="6">
         <v>5100</v>
@@ -4241,14 +4241,14 @@
       </c>
       <c r="BC24" s="10">
         <f t="shared" si="20"/>
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="BD24" s="7">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="BE24" s="9">
         <f t="shared" si="21"/>
-        <v>0.8056862745098039</v>
+        <v>0.80588235294117649</v>
       </c>
       <c r="BF24" s="6">
         <v>5225</v>
@@ -4258,14 +4258,14 @@
       </c>
       <c r="BH24" s="10">
         <f t="shared" si="22"/>
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="BI24" s="7">
-        <v>4197</v>
+        <v>4199</v>
       </c>
       <c r="BJ24" s="9">
         <f t="shared" si="23"/>
-        <v>0.80325358851674644</v>
+        <v>0.80363636363636359</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="BC26" s="10">
         <f t="shared" si="20"/>
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="BD26" s="7">
-        <v>19144</v>
+        <v>19145</v>
       </c>
       <c r="BE26" s="9">
         <f t="shared" si="21"/>
-        <v>0.8120122158126909</v>
+        <v>0.81205463182897863</v>
       </c>
       <c r="BF26" s="6">
         <v>23703</v>
@@ -4707,14 +4707,14 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" si="0"/>
-        <v>75971</v>
+        <v>75972</v>
       </c>
       <c r="F27" s="7">
-        <v>104528</v>
+        <v>104529</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" si="1"/>
-        <v>0.82745299821887985</v>
+        <v>0.82746091430833169</v>
       </c>
       <c r="H27" s="4">
         <v>130935</v>
@@ -4809,14 +4809,14 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="12"/>
-        <v>56535</v>
+        <v>56537</v>
       </c>
       <c r="AJ27" s="7">
-        <v>117014</v>
+        <v>117016</v>
       </c>
       <c r="AK27" s="9">
         <f t="shared" si="13"/>
-        <v>0.79946708571038161</v>
+        <v>0.79948075017934617</v>
       </c>
       <c r="AL27" s="4">
         <v>148564</v>
@@ -4826,14 +4826,14 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="14"/>
-        <v>51226</v>
+        <v>51228</v>
       </c>
       <c r="AO27" s="7">
-        <v>116562</v>
+        <v>116564</v>
       </c>
       <c r="AP27" s="9">
         <f t="shared" si="15"/>
-        <v>0.78459115263455481</v>
+        <v>0.78460461484612687</v>
       </c>
       <c r="AQ27" s="4">
         <v>150627</v>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="16"/>
-        <v>55102</v>
+        <v>55104</v>
       </c>
       <c r="AT27" s="7">
-        <v>117515</v>
+        <v>117517</v>
       </c>
       <c r="AU27" s="9">
         <f t="shared" si="17"/>
-        <v>0.78017221348098287</v>
+        <v>0.78018549131297843</v>
       </c>
       <c r="AV27" s="6">
         <v>152840</v>
@@ -4860,14 +4860,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>59010</v>
+        <v>59012</v>
       </c>
       <c r="AY27" s="7">
-        <v>118340</v>
+        <v>118342</v>
       </c>
       <c r="AZ27" s="9">
         <f t="shared" si="19"/>
-        <v>0.77427375032713952</v>
+        <v>0.77428683590683067</v>
       </c>
       <c r="BA27" s="6">
         <v>154902</v>
@@ -4877,14 +4877,14 @@
       </c>
       <c r="BC27" s="10">
         <f t="shared" si="20"/>
-        <v>46453</v>
+        <v>46455</v>
       </c>
       <c r="BD27" s="7">
-        <v>119500</v>
+        <v>119502</v>
       </c>
       <c r="BE27" s="9">
         <f t="shared" si="21"/>
-        <v>0.7714555008973415</v>
+        <v>0.77146841228647789</v>
       </c>
       <c r="BF27" s="6">
         <v>157244</v>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>73059</v>
+        <v>73061</v>
       </c>
       <c r="BI27" s="7">
-        <v>120362</v>
+        <v>120364</v>
       </c>
       <c r="BJ27" s="9">
         <f t="shared" si="23"/>
-        <v>0.76544733026379386</v>
+        <v>0.76546004935005474</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="T30" s="10">
         <f t="shared" si="6"/>
-        <v>50510</v>
+        <v>50511</v>
       </c>
       <c r="U30" s="7">
-        <v>176652</v>
+        <v>176653</v>
       </c>
       <c r="V30" s="9">
         <f t="shared" si="7"/>
-        <v>0.8577130177658443</v>
+        <v>0.85771787314827852</v>
       </c>
       <c r="W30" s="4">
         <v>211137</v>
@@ -5411,14 +5411,14 @@
       </c>
       <c r="Y30" s="10">
         <f t="shared" si="8"/>
-        <v>71111</v>
+        <v>71112</v>
       </c>
       <c r="Z30" s="7">
-        <v>180179</v>
+        <v>180180</v>
       </c>
       <c r="AA30" s="9">
         <f t="shared" si="9"/>
-        <v>0.85337482298223433</v>
+        <v>0.85337955924352438</v>
       </c>
       <c r="AB30" s="4">
         <v>214949</v>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="10"/>
-        <v>56772</v>
+        <v>56773</v>
       </c>
       <c r="AE30" s="7">
-        <v>183065</v>
+        <v>183066</v>
       </c>
       <c r="AF30" s="9">
         <f t="shared" si="11"/>
-        <v>0.85166713964707907</v>
+        <v>0.85167179191343068</v>
       </c>
       <c r="AG30" s="4">
         <v>218841</v>
@@ -5445,14 +5445,14 @@
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="12"/>
-        <v>65123</v>
+        <v>65124</v>
       </c>
       <c r="AJ30" s="7">
-        <v>186058</v>
+        <v>186059</v>
       </c>
       <c r="AK30" s="9">
         <f t="shared" si="13"/>
-        <v>0.85019717511800807</v>
+        <v>0.85020174464565601</v>
       </c>
       <c r="AL30" s="4">
         <v>222034</v>
@@ -5462,14 +5462,14 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="14"/>
-        <v>58879</v>
+        <v>58880</v>
       </c>
       <c r="AO30" s="7">
-        <v>185949</v>
+        <v>185950</v>
       </c>
       <c r="AP30" s="9">
         <f t="shared" si="15"/>
-        <v>0.83747984542907838</v>
+        <v>0.83748434924380954</v>
       </c>
       <c r="AQ30" s="4">
         <v>223141</v>
@@ -5674,14 +5674,14 @@
       </c>
       <c r="AN31" s="10">
         <f t="shared" si="14"/>
-        <v>35550</v>
+        <v>35551</v>
       </c>
       <c r="AO31" s="7">
-        <v>93148</v>
+        <v>93149</v>
       </c>
       <c r="AP31" s="9">
         <f t="shared" si="15"/>
-        <v>0.91720823978888499</v>
+        <v>0.91721808657292525</v>
       </c>
       <c r="AQ31" s="4">
         <v>101564</v>
@@ -5979,14 +5979,14 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="0"/>
-        <v>401553</v>
+        <v>401555</v>
       </c>
       <c r="F33" s="7">
-        <v>722981</v>
+        <v>722983</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="1"/>
-        <v>0.94659889730768676</v>
+        <v>0.94660151590733821</v>
       </c>
       <c r="H33" s="4">
         <v>790674</v>
@@ -5996,14 +5996,14 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v>169977</v>
+        <v>169979</v>
       </c>
       <c r="K33" s="7">
-        <v>735195</v>
+        <v>735197</v>
       </c>
       <c r="L33" s="9">
         <f t="shared" si="3"/>
-        <v>0.92983328147883959</v>
+        <v>0.92983581096634016</v>
       </c>
       <c r="M33" s="4">
         <v>801034</v>
@@ -6013,14 +6013,14 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="4"/>
-        <v>180420</v>
+        <v>180422</v>
       </c>
       <c r="P33" s="7">
-        <v>744297</v>
+        <v>744299</v>
       </c>
       <c r="Q33" s="9">
         <f t="shared" si="5"/>
-        <v>0.92917029739062262</v>
+        <v>0.92917279416354359</v>
       </c>
       <c r="R33" s="4">
         <v>811485</v>
@@ -6030,14 +6030,14 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="6"/>
-        <v>138452</v>
+        <v>138454</v>
       </c>
       <c r="U33" s="7">
-        <v>751889</v>
+        <v>751891</v>
       </c>
       <c r="V33" s="9">
         <f t="shared" si="7"/>
-        <v>0.92655933258162504</v>
+        <v>0.92656179719896237</v>
       </c>
       <c r="W33" s="4">
         <v>819064</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>204481</v>
+        <v>204483</v>
       </c>
       <c r="Z33" s="7">
-        <v>761132</v>
+        <v>761134</v>
       </c>
       <c r="AA33" s="9">
         <f t="shared" si="9"/>
-        <v>0.92927048435775472</v>
+        <v>0.92927292616938362</v>
       </c>
       <c r="AB33" s="4">
         <v>823883</v>
@@ -6064,14 +6064,14 @@
       </c>
       <c r="AD33" s="10">
         <f t="shared" si="10"/>
-        <v>153442</v>
+        <v>153445</v>
       </c>
       <c r="AE33" s="7">
-        <v>767918</v>
+        <v>767921</v>
       </c>
       <c r="AF33" s="9">
         <f t="shared" si="11"/>
-        <v>0.93207166551561327</v>
+        <v>0.9320753068093407</v>
       </c>
       <c r="AG33" s="4">
         <v>827687</v>
@@ -6081,14 +6081,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>226202</v>
+        <v>226204</v>
       </c>
       <c r="AJ33" s="7">
-        <v>773752</v>
+        <v>773754</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="13"/>
-        <v>0.93483647804061198</v>
+        <v>0.93483889441298462</v>
       </c>
       <c r="AL33" s="4">
         <v>833066</v>
@@ -6098,14 +6098,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>170647</v>
+        <v>170650</v>
       </c>
       <c r="AO33" s="7">
-        <v>774386</v>
+        <v>774389</v>
       </c>
       <c r="AP33" s="9">
         <f t="shared" si="15"/>
-        <v>0.92956140329817805</v>
+        <v>0.92956500445342871</v>
       </c>
       <c r="AQ33" s="4">
         <v>838229</v>
@@ -6115,14 +6115,14 @@
       </c>
       <c r="AS33" s="10">
         <f t="shared" si="16"/>
-        <v>188060</v>
+        <v>188063</v>
       </c>
       <c r="AT33" s="7">
-        <v>782816</v>
+        <v>782819</v>
       </c>
       <c r="AU33" s="9">
         <f t="shared" si="17"/>
-        <v>0.93389276677375754</v>
+        <v>0.93389634574799962</v>
       </c>
       <c r="AV33" s="6">
         <v>846900</v>
@@ -6132,14 +6132,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>217580</v>
+        <v>217583</v>
       </c>
       <c r="AY33" s="7">
-        <v>788688</v>
+        <v>788691</v>
       </c>
       <c r="AZ33" s="9">
         <f t="shared" si="19"/>
-        <v>0.93126461211477152</v>
+        <v>0.93126815444562527</v>
       </c>
       <c r="BA33" s="6">
         <v>854421</v>
@@ -6149,14 +6149,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>134195</v>
+        <v>134198</v>
       </c>
       <c r="BD33" s="7">
-        <v>795542</v>
+        <v>795545</v>
       </c>
       <c r="BE33" s="9">
         <f t="shared" si="21"/>
-        <v>0.93108900647338955</v>
+        <v>0.93109251762304535</v>
       </c>
       <c r="BF33" s="6">
         <v>864165</v>
@@ -6166,14 +6166,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>281125</v>
+        <v>281128</v>
       </c>
       <c r="BI33" s="7">
-        <v>802666</v>
+        <v>802669</v>
       </c>
       <c r="BJ33" s="9">
         <f t="shared" si="23"/>
-        <v>0.92883419254424793</v>
+        <v>0.92883766410349877</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6615,14 +6615,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>635204</v>
+        <v>635206</v>
       </c>
       <c r="F36" s="7">
-        <v>1117305</v>
+        <v>1117307</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="1"/>
-        <v>0.90621639114502484</v>
+        <v>0.90621801329187124</v>
       </c>
       <c r="H36" s="4">
         <v>1268548</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>364150</v>
+        <v>364151</v>
       </c>
       <c r="K36" s="7">
-        <v>1135868</v>
+        <v>1135869</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="3"/>
-        <v>0.89540797825545426</v>
+        <v>0.89540876655830126</v>
       </c>
       <c r="M36" s="4">
         <v>1291465</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>366230</v>
+        <v>366231</v>
       </c>
       <c r="P36" s="7">
-        <v>1150172</v>
+        <v>1150173</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="5"/>
-        <v>0.89059478963812411</v>
+        <v>0.89059556395256545</v>
       </c>
       <c r="R36" s="4">
         <v>1304709</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>303566</v>
+        <v>303567</v>
       </c>
       <c r="U36" s="7">
-        <v>1161623</v>
+        <v>1161624</v>
       </c>
       <c r="V36" s="9">
         <f t="shared" si="7"/>
-        <v>0.89033110065156296</v>
+        <v>0.89033186710599832</v>
       </c>
       <c r="W36" s="4">
         <v>1322652</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>444961</v>
+        <v>444962</v>
       </c>
       <c r="Z36" s="7">
-        <v>1173314</v>
+        <v>1173315</v>
       </c>
       <c r="AA36" s="9">
         <f t="shared" si="9"/>
-        <v>0.88709199396364269</v>
+        <v>0.88709275002041355</v>
       </c>
       <c r="AB36" s="4">
         <v>1322160</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>336123</v>
+        <v>336124</v>
       </c>
       <c r="AE36" s="7">
-        <v>1183574</v>
+        <v>1183575</v>
       </c>
       <c r="AF36" s="9">
         <f t="shared" si="11"/>
-        <v>0.89518212621770432</v>
+        <v>0.89518288255581779</v>
       </c>
       <c r="AG36" s="4">
         <v>1336822</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>409286</v>
+        <v>409287</v>
       </c>
       <c r="AJ36" s="7">
-        <v>1192846</v>
+        <v>1192847</v>
       </c>
       <c r="AK36" s="9">
         <f t="shared" si="13"/>
-        <v>0.89229979757963285</v>
+        <v>0.89230054562237904</v>
       </c>
       <c r="AL36" s="4">
         <v>1349209</v>
@@ -6734,14 +6734,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>349943</v>
+        <v>349945</v>
       </c>
       <c r="AO36" s="7">
-        <v>1189351</v>
+        <v>1189353</v>
       </c>
       <c r="AP36" s="9">
         <f t="shared" si="15"/>
-        <v>0.88151724454847247</v>
+        <v>0.8815187268985013</v>
       </c>
       <c r="AQ36" s="4">
         <v>1349417</v>
@@ -6751,14 +6751,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>371131</v>
+        <v>371132</v>
       </c>
       <c r="AT36" s="7">
-        <v>1201605</v>
+        <v>1201606</v>
       </c>
       <c r="AU36" s="9">
         <f t="shared" si="17"/>
-        <v>0.89046232558208471</v>
+        <v>0.89046306664285391</v>
       </c>
       <c r="AV36" s="6">
         <v>1347780</v>
@@ -6768,14 +6768,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>460663</v>
+        <v>460664</v>
       </c>
       <c r="AY36" s="7">
-        <v>1211606</v>
+        <v>1211607</v>
       </c>
       <c r="AZ36" s="9">
         <f t="shared" si="19"/>
-        <v>0.89896422264761311</v>
+        <v>0.89896496460846731</v>
       </c>
       <c r="BA36" s="6">
         <v>1364152</v>
@@ -6785,14 +6785,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>293545</v>
+        <v>293546</v>
       </c>
       <c r="BD36" s="7">
-        <v>1221220</v>
+        <v>1221221</v>
       </c>
       <c r="BE36" s="9">
         <f t="shared" si="21"/>
-        <v>0.8952228197444273</v>
+        <v>0.89522355280056765</v>
       </c>
       <c r="BF36" s="6">
         <v>1384075</v>
@@ -6802,14 +6802,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="22"/>
-        <v>511478</v>
+        <v>511479</v>
       </c>
       <c r="BI36" s="7">
-        <v>1229540</v>
+        <v>1229541</v>
       </c>
       <c r="BJ36" s="9">
         <f t="shared" si="23"/>
-        <v>0.88834781352166614</v>
+        <v>0.88834853602586561</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6827,14 +6827,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>356715</v>
+        <v>356718</v>
       </c>
       <c r="F37" s="7">
-        <v>552282</v>
+        <v>552285</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="1"/>
-        <v>0.89440553211818907</v>
+        <v>0.89441039053580251</v>
       </c>
       <c r="H37" s="4">
         <v>636289</v>
@@ -6844,14 +6844,14 @@
       </c>
       <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v>165071</v>
+        <v>165072</v>
       </c>
       <c r="K37" s="7">
-        <v>560834</v>
+        <v>560835</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="3"/>
-        <v>0.88141394869312528</v>
+        <v>0.88141552030602444</v>
       </c>
       <c r="M37" s="4">
         <v>650458</v>
@@ -6861,14 +6861,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>166954</v>
+        <v>166955</v>
       </c>
       <c r="P37" s="7">
-        <v>569069</v>
+        <v>569070</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="5"/>
-        <v>0.87487431932576742</v>
+        <v>0.87487585670404544</v>
       </c>
       <c r="R37" s="4">
         <v>663657</v>
@@ -6878,14 +6878,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>133643</v>
+        <v>133644</v>
       </c>
       <c r="U37" s="7">
-        <v>578194</v>
+        <v>578195</v>
       </c>
       <c r="V37" s="9">
         <f t="shared" si="7"/>
-        <v>0.87122414138628845</v>
+        <v>0.87122564818874815</v>
       </c>
       <c r="W37" s="4">
         <v>677316</v>
@@ -6895,14 +6895,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>185292</v>
+        <v>185293</v>
       </c>
       <c r="Z37" s="7">
-        <v>587380</v>
+        <v>587381</v>
       </c>
       <c r="AA37" s="9">
         <f t="shared" si="9"/>
-        <v>0.86721707445269269</v>
+        <v>0.8672185508684277</v>
       </c>
       <c r="AB37" s="4">
         <v>682420</v>
@@ -6912,14 +6912,14 @@
       </c>
       <c r="AD37" s="10">
         <f t="shared" si="10"/>
-        <v>150860</v>
+        <v>150862</v>
       </c>
       <c r="AE37" s="7">
-        <v>594947</v>
+        <v>594949</v>
       </c>
       <c r="AF37" s="9">
         <f t="shared" si="11"/>
-        <v>0.87181940740306552</v>
+        <v>0.8718223381495267</v>
       </c>
       <c r="AG37" s="4">
         <v>691854</v>
@@ -6929,14 +6929,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>185429</v>
+        <v>185430</v>
       </c>
       <c r="AJ37" s="7">
-        <v>603112</v>
+        <v>603113</v>
       </c>
       <c r="AK37" s="9">
         <f t="shared" si="13"/>
-        <v>0.87173305350550834</v>
+        <v>0.87173449889716614</v>
       </c>
       <c r="AL37" s="4">
         <v>698331</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>163065</v>
+        <v>163066</v>
       </c>
       <c r="AO37" s="7">
-        <v>603944</v>
+        <v>603945</v>
       </c>
       <c r="AP37" s="9">
         <f t="shared" si="15"/>
-        <v>0.86483916652704806</v>
+        <v>0.86484059851273964</v>
       </c>
       <c r="AQ37" s="4">
         <v>700400</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>175162</v>
+        <v>175163</v>
       </c>
       <c r="AT37" s="7">
-        <v>611991</v>
+        <v>611992</v>
       </c>
       <c r="AU37" s="9">
         <f t="shared" si="17"/>
-        <v>0.87377355796687606</v>
+        <v>0.87377498572244428</v>
       </c>
       <c r="AV37" s="6">
         <v>698615</v>
@@ -6980,14 +6980,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>212638</v>
+        <v>212639</v>
       </c>
       <c r="AY37" s="7">
-        <v>619451</v>
+        <v>619452</v>
       </c>
       <c r="AZ37" s="9">
         <f t="shared" si="19"/>
-        <v>0.88668436835739284</v>
+        <v>0.88668579976095563</v>
       </c>
       <c r="BA37" s="6">
         <v>701194</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>123323</v>
+        <v>123324</v>
       </c>
       <c r="BD37" s="7">
-        <v>626359</v>
+        <v>626360</v>
       </c>
       <c r="BE37" s="9">
         <f t="shared" si="21"/>
-        <v>0.89327489967113238</v>
+        <v>0.89327632580997551</v>
       </c>
       <c r="BF37" s="6">
         <v>706472</v>
@@ -7675,14 +7675,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>385856</v>
+        <v>385862</v>
       </c>
       <c r="F41" s="7">
-        <v>690942</v>
+        <v>690948</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="1"/>
-        <v>0.85040062031532693</v>
+        <v>0.8504080050216003</v>
       </c>
       <c r="H41" s="4">
         <v>835051</v>
@@ -7692,14 +7692,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>211148</v>
+        <v>211154</v>
       </c>
       <c r="K41" s="7">
-        <v>701668</v>
+        <v>701674</v>
       </c>
       <c r="L41" s="9">
         <f t="shared" si="3"/>
-        <v>0.84026963622581141</v>
+        <v>0.84027682141569793</v>
       </c>
       <c r="M41" s="4">
         <v>852643</v>
@@ -7709,14 +7709,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>211057</v>
+        <v>211062</v>
       </c>
       <c r="P41" s="7">
-        <v>709927</v>
+        <v>709932</v>
       </c>
       <c r="Q41" s="9">
         <f t="shared" si="5"/>
-        <v>0.83261927911212552</v>
+        <v>0.83262514323110615</v>
       </c>
       <c r="R41" s="4">
         <v>868359</v>
@@ -7726,14 +7726,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171930</v>
+        <v>171939</v>
       </c>
       <c r="U41" s="7">
-        <v>719477</v>
+        <v>719486</v>
       </c>
       <c r="V41" s="9">
         <f t="shared" si="7"/>
-        <v>0.8285478701781176</v>
+        <v>0.82855823455506306</v>
       </c>
       <c r="W41" s="4">
         <v>879806</v>
@@ -7743,14 +7743,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>230061</v>
+        <v>230068</v>
       </c>
       <c r="Z41" s="7">
-        <v>727720</v>
+        <v>727727</v>
       </c>
       <c r="AA41" s="9">
         <f t="shared" si="9"/>
-        <v>0.82713689154199899</v>
+        <v>0.82714484784145592</v>
       </c>
       <c r="AB41" s="4">
         <v>882248</v>
@@ -7760,14 +7760,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>187414</v>
+        <v>187421</v>
       </c>
       <c r="AE41" s="7">
-        <v>735477</v>
+        <v>735484</v>
       </c>
       <c r="AF41" s="9">
         <f t="shared" si="11"/>
-        <v>0.83363974755397574</v>
+        <v>0.83364768183095905</v>
       </c>
       <c r="AG41" s="4">
         <v>877145</v>
@@ -7777,14 +7777,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>242423</v>
+        <v>242429</v>
       </c>
       <c r="AJ41" s="7">
-        <v>743285</v>
+        <v>743291</v>
       </c>
       <c r="AK41" s="9">
         <f t="shared" si="13"/>
-        <v>0.84739125230150092</v>
+        <v>0.84739809267566935</v>
       </c>
       <c r="AL41" s="4">
         <v>875890</v>
@@ -7794,14 +7794,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>205249</v>
+        <v>205254</v>
       </c>
       <c r="AO41" s="7">
-        <v>742094</v>
+        <v>742099</v>
       </c>
       <c r="AP41" s="9">
         <f t="shared" si="15"/>
-        <v>0.84724565870143509</v>
+        <v>0.8472513671808104</v>
       </c>
       <c r="AQ41" s="4">
         <v>865402</v>
@@ -7811,14 +7811,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>247890</v>
+        <v>247895</v>
       </c>
       <c r="AT41" s="7">
-        <v>748358</v>
+        <v>748363</v>
       </c>
       <c r="AU41" s="9">
         <f t="shared" si="17"/>
-        <v>0.8647518725401605</v>
+        <v>0.86475765020187145</v>
       </c>
       <c r="AV41" s="6">
         <v>863602</v>
@@ -7828,14 +7828,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>252926</v>
+        <v>252932</v>
       </c>
       <c r="AY41" s="7">
-        <v>753204</v>
+        <v>753210</v>
       </c>
       <c r="AZ41" s="9">
         <f t="shared" si="19"/>
-        <v>0.87216565038061511</v>
+        <v>0.87217259802547931</v>
       </c>
       <c r="BA41" s="6">
         <v>853803</v>
@@ -7845,14 +7845,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>156262</v>
+        <v>156266</v>
       </c>
       <c r="BD41" s="7">
-        <v>759999</v>
+        <v>760003</v>
       </c>
       <c r="BE41" s="9">
         <f t="shared" si="21"/>
-        <v>0.89013390676772042</v>
+        <v>0.89013859168918352</v>
       </c>
       <c r="BF41" s="6">
         <v>867754</v>
@@ -7862,14 +7862,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="22"/>
-        <v>339125</v>
+        <v>339130</v>
       </c>
       <c r="BI41" s="7">
-        <v>767271</v>
+        <v>767276</v>
       </c>
       <c r="BJ41" s="9">
         <f t="shared" si="23"/>
-        <v>0.88420335717265497</v>
+        <v>0.88420911917432821</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8523,14 +8523,14 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" si="0"/>
-        <v>119237</v>
+        <v>119238</v>
       </c>
       <c r="F45" s="7">
-        <v>212496</v>
+        <v>212497</v>
       </c>
       <c r="G45" s="9">
         <f t="shared" si="1"/>
-        <v>0.88523401862150841</v>
+        <v>0.88523818450707159</v>
       </c>
       <c r="H45" s="4">
         <v>247611</v>
@@ -8574,14 +8574,14 @@
       </c>
       <c r="T45" s="10">
         <f t="shared" si="6"/>
-        <v>50480</v>
+        <v>50481</v>
       </c>
       <c r="U45" s="7">
-        <v>221886</v>
+        <v>221887</v>
       </c>
       <c r="V45" s="9">
         <f t="shared" si="7"/>
-        <v>0.86440559113645921</v>
+        <v>0.86440948685584285</v>
       </c>
       <c r="W45" s="4">
         <v>257705</v>
@@ -9121,10 +9121,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="24"/>
+      <c r="B48" s="21"/>
       <c r="C48" s="13">
         <f>SUM(C10:C47)</f>
         <v>8817798</v>
@@ -9135,15 +9135,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>4591868</v>
+        <v>4591886</v>
       </c>
       <c r="F48" s="13">
         <f>SUM(F10:F47)</f>
-        <v>8024186</v>
+        <v>8024204</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.90999884551676058</v>
+        <v>0.91000088684272418</v>
       </c>
       <c r="H48" s="13">
         <f>SUM(H10:H47)</f>
@@ -9155,15 +9155,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>2452788</v>
+        <v>2452800</v>
       </c>
       <c r="K48" s="13">
         <f>SUM(K10:K47)</f>
-        <v>8179228</v>
+        <v>8179240</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.89661816980766607</v>
+        <v>0.89661948526409263</v>
       </c>
       <c r="M48" s="13">
         <f>SUM(M10:M47)</f>
@@ -9175,15 +9175,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2507202</v>
+        <v>2507213</v>
       </c>
       <c r="P48" s="13">
         <f>SUM(P10:P47)</f>
-        <v>8297525</v>
+        <v>8297536</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.89060676998640076</v>
+        <v>0.89060795066069465</v>
       </c>
       <c r="R48" s="13">
         <f>SUM(R10:R47)</f>
@@ -9195,15 +9195,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>2026668</v>
+        <v>2026686</v>
       </c>
       <c r="U48" s="13">
         <f>SUM(U10:U47)</f>
-        <v>8410318</v>
+        <v>8410336</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.88807471625448953</v>
+        <v>0.88807661693706696</v>
       </c>
       <c r="W48" s="13">
         <f>SUM(W10:W47)</f>
@@ -9215,15 +9215,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>2872132</v>
+        <v>2872148</v>
       </c>
       <c r="Z48" s="13">
         <f>SUM(Z10:Z47)</f>
-        <v>8522372</v>
+        <v>8522388</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.8863369765996244</v>
+        <v>0.8863386406189403</v>
       </c>
       <c r="AB48" s="13">
         <f>SUM(AB10:AB47)</f>
@@ -9235,15 +9235,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2248006</v>
+        <v>2248023</v>
       </c>
       <c r="AE48" s="13">
         <f>SUM(AE10:AE47)</f>
-        <v>8617260</v>
+        <v>8617277</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.89231093897541525</v>
+        <v>0.89231269931291957</v>
       </c>
       <c r="AG48" s="13">
         <f>SUM(AG10:AG47)</f>
@@ -9255,15 +9255,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2832589</v>
+        <v>2832605</v>
       </c>
       <c r="AJ48" s="13">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8715254</v>
+        <v>8715270</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.8931701276043118</v>
+        <v>0.89317176734103576</v>
       </c>
       <c r="AL48" s="13">
         <f>SUM(AL10:AL47)</f>
@@ -9275,15 +9275,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2422694</v>
+        <v>2422713</v>
       </c>
       <c r="AO48" s="13">
         <f>SUM(AO10:AO47)</f>
-        <v>8713055</v>
+        <v>8713074</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.88487550835843076</v>
+        <v>0.88487743794967733</v>
       </c>
       <c r="AQ48" s="13">
         <f>SUM(AQ10:AQ47)</f>
@@ -9295,15 +9295,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>2607071</v>
+        <v>2607088</v>
       </c>
       <c r="AT48" s="13">
         <f>SUM(AT10:AT47)</f>
-        <v>8806527</v>
+        <v>8806544</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.88936878086309257</v>
+        <v>0.88937049768849652</v>
       </c>
       <c r="AV48" s="13">
         <f>SUM(AV10:AV47)</f>
@@ -9315,15 +9315,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>3160752</v>
+        <v>3160769</v>
       </c>
       <c r="AY48" s="13">
         <f>SUM(AY10:AY47)</f>
-        <v>8886753</v>
+        <v>8886770</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.89111347558053589</v>
+        <v>0.8911151802446674</v>
       </c>
       <c r="BA48" s="13">
         <f>SUM(BA10:BA47)</f>
@@ -9335,15 +9335,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2003750</v>
+        <v>2003765</v>
       </c>
       <c r="BD48" s="13">
         <f>SUM(BD10:BD47)</f>
-        <v>8967004</v>
+        <v>8967019</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.89185912113275512</v>
+        <v>0.89186061303426611</v>
       </c>
       <c r="BF48" s="13">
         <f>SUM(BF10:BF47)</f>
@@ -9355,18 +9355,18 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>3828586</v>
+        <v>3828602</v>
       </c>
       <c r="BI48" s="13">
         <f>SUM(BI10:BI47)</f>
-        <v>9043413</v>
+        <v>9043429</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.88878944013441596</v>
+        <v>0.88879101261938842</v>
       </c>
     </row>
-    <row r="49" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:62" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -9429,9 +9429,8 @@
       <c r="BH49"/>
       <c r="BI49"/>
       <c r="BJ49"/>
-      <c r="BK49"/>
     </row>
-    <row r="50" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:62" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
@@ -9494,9 +9493,8 @@
       <c r="BH50"/>
       <c r="BI50"/>
       <c r="BJ50"/>
-      <c r="BK50"/>
     </row>
-    <row r="51" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
@@ -9560,7 +9558,7 @@
       <c r="BI51"/>
       <c r="BJ51"/>
     </row>
-    <row r="52" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
@@ -9624,7 +9622,7 @@
       <c r="BI52"/>
       <c r="BJ52"/>
     </row>
-    <row r="53" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
@@ -9688,145 +9686,25 @@
       <c r="BI53"/>
       <c r="BJ53"/>
     </row>
-    <row r="54" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54"/>
-      <c r="R54"/>
-      <c r="S54"/>
-      <c r="T54"/>
-      <c r="U54"/>
-      <c r="V54"/>
-      <c r="W54"/>
-      <c r="X54"/>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AA54"/>
-      <c r="AB54"/>
-      <c r="AC54"/>
-      <c r="AD54"/>
-      <c r="AE54"/>
-      <c r="AF54"/>
-      <c r="AG54"/>
-      <c r="AH54"/>
-      <c r="AI54"/>
-      <c r="AJ54"/>
-      <c r="AK54"/>
-      <c r="AL54"/>
-      <c r="AM54"/>
-      <c r="AN54"/>
-      <c r="AO54"/>
-      <c r="AP54"/>
-      <c r="AQ54"/>
-      <c r="AR54"/>
-      <c r="AS54"/>
-      <c r="AT54"/>
-      <c r="AU54"/>
-      <c r="AV54"/>
-      <c r="AW54"/>
-      <c r="AX54"/>
-      <c r="AY54"/>
-      <c r="AZ54"/>
-      <c r="BA54"/>
-      <c r="BB54"/>
-      <c r="BC54"/>
-      <c r="BD54"/>
-      <c r="BE54"/>
-      <c r="BF54"/>
-      <c r="BG54"/>
-      <c r="BH54"/>
-      <c r="BI54"/>
-      <c r="BJ54"/>
-    </row>
-    <row r="55" spans="1:63" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55"/>
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55"/>
-      <c r="R55"/>
-      <c r="S55"/>
-      <c r="T55"/>
-      <c r="U55"/>
-      <c r="V55"/>
-      <c r="W55"/>
-      <c r="X55"/>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AA55"/>
-      <c r="AB55"/>
-      <c r="AC55"/>
-      <c r="AD55"/>
-      <c r="AE55"/>
-      <c r="AF55"/>
-      <c r="AG55"/>
-      <c r="AH55"/>
-      <c r="AI55"/>
-      <c r="AJ55"/>
-      <c r="AK55"/>
-      <c r="AL55"/>
-      <c r="AM55"/>
-      <c r="AN55"/>
-      <c r="AO55"/>
-      <c r="AP55"/>
-      <c r="AQ55"/>
-      <c r="AR55"/>
-      <c r="AS55"/>
-      <c r="AT55"/>
-      <c r="AU55"/>
-      <c r="AV55"/>
-      <c r="AW55"/>
-      <c r="AX55"/>
-      <c r="AY55"/>
-      <c r="AZ55"/>
-      <c r="BA55"/>
-      <c r="BB55"/>
-      <c r="BC55"/>
-      <c r="BD55"/>
-      <c r="BE55"/>
-      <c r="BF55"/>
-      <c r="BG55"/>
-      <c r="BH55"/>
-      <c r="BI55"/>
-      <c r="BJ55"/>
-    </row>
-    <row r="56" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A56" s="17" t="s">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A54" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
@@ -9838,14 +9716,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
